--- a/271025_Results_Med/MNL/mnl_med_concomunas_OR.xlsx
+++ b/271025_Results_Med/MNL/mnl_med_concomunas_OR.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:G217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -413,7 +413,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>-461.719</v>
+        <v>-37.032</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -431,7 +431,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>1.723143609200713E+99</v>
+        <v>1207.971</v>
+      </c>
+      <c r="D3">
+        <v>0.008</v>
+      </c>
+      <c r="E3">
+        <v>192530615.423</v>
+      </c>
+      <c r="F3">
+        <v>1.161</v>
+      </c>
+      <c r="G3">
+        <v>0.2456</v>
       </c>
     </row>
     <row r="4">
@@ -446,16 +458,16 @@
         </is>
       </c>
       <c r="C4">
-        <v>2.41478165029674E+209</v>
+        <v>890363585.2130001</v>
       </c>
       <c r="D4">
-        <v>2.147440373236616E+209</v>
+        <v>6734914.727</v>
       </c>
       <c r="E4">
-        <v>2.715405042805041E+209</v>
+        <v>117707104846.702</v>
       </c>
       <c r="F4">
-        <v>8053.701</v>
+        <v>8.269</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -469,11 +481,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>`p12_dificultad_binaria_Con alguna dificultad`</t>
+          <t>`educacion_Primaria o menos`</t>
         </is>
       </c>
       <c r="C5">
-        <v>9.23718287130113E+53</v>
+        <v>31301152044319.31</v>
+      </c>
+      <c r="D5">
+        <v>184383066284.921</v>
+      </c>
+      <c r="E5">
+        <v>5313731564630803</v>
+      </c>
+      <c r="F5">
+        <v>11.862</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -487,23 +511,17 @@
           <t>`p15_autos_agregado_1 auto`</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+      <c r="C6">
+        <v>3.017592729863068E+35</v>
+      </c>
+      <c r="D6">
+        <v>6.724557822559115E+28</v>
+      </c>
+      <c r="E6">
+        <v>1.354121136823996E+42</v>
       </c>
       <c r="F6">
-        <v>523.624</v>
+        <v>10.454</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -520,10 +538,20 @@
           <t>`p15_autos_agregado_2 o más autos`</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+      <c r="C7">
+        <v>1.501268322447324E+54</v>
+      </c>
+      <c r="D7">
+        <v>1.758983252531852E+49</v>
+      </c>
+      <c r="E7">
+        <v>1.281312128890222E+59</v>
+      </c>
+      <c r="F7">
+        <v>21.533</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -538,19 +566,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>6.5757581906067E+137</v>
+        <v>18.007</v>
       </c>
       <c r="D8">
-        <v>6.57575819058988E+137</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>6.575758190623521E+137</v>
+        <v>2320794.389</v>
       </c>
       <c r="F8">
-        <v>245852582914263</v>
+        <v>0.482</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.6301</v>
       </c>
     </row>
     <row r="9">
@@ -564,23 +592,17 @@
           <t>`p16_motos_agregado_Sin motocicletas`</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+      <c r="C9">
+        <v>6.23748983527558E+40</v>
+      </c>
+      <c r="D9">
+        <v>1.850520602391738E+34</v>
+      </c>
+      <c r="E9">
+        <v>2.102450488520964E+47</v>
       </c>
       <c r="F9">
-        <v>538.412</v>
+        <v>12.249</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -600,6 +622,18 @@
       <c r="C10">
         <v>0</v>
       </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>-9934782179.813999</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -622,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>-2.204797657619698E+16</v>
+        <v>-7.497</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -649,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>-6.13075817544395E+20</v>
+        <v>-14.664</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -669,18 +703,6 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>-3.31715087093608E+21</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -693,23 +715,17 @@
           <t>`p19comuna_Comuna 13 - San Javier`</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+      <c r="C14">
+        <v>1.699661552282557E+28</v>
+      </c>
+      <c r="D14">
+        <v>9.04080915210474E+25</v>
+      </c>
+      <c r="E14">
+        <v>3.195343849986053E+30</v>
       </c>
       <c r="F14">
-        <v>3.721226042676262E+16</v>
+        <v>24.331</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -733,13 +749,13 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>7551.072</v>
       </c>
       <c r="F15">
-        <v>-7.958813766694333E+20</v>
+        <v>-0.909</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>0.3634</v>
       </c>
     </row>
     <row r="16">
@@ -754,7 +770,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>1.283133820856334E+259</v>
+        <v>1.689340795034315E+20</v>
+      </c>
+      <c r="D16">
+        <v>4267562273859306</v>
+      </c>
+      <c r="E16">
+        <v>6.687359524308279E+24</v>
+      </c>
+      <c r="F16">
+        <v>8.622999999999999</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -778,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>-6.37904208581429E+21</v>
+        <v>-32873.105</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -796,16 +824,16 @@
         </is>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>147666257.11</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>30758.01</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>708931534334.424</v>
       </c>
       <c r="F18">
-        <v>-12337.168</v>
+        <v>4.349</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -823,7 +851,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>2.880912757681664E+110</v>
+        <v>5.287</v>
+      </c>
+      <c r="D19">
+        <v>0.004</v>
+      </c>
+      <c r="E19">
+        <v>6352.578</v>
+      </c>
+      <c r="F19">
+        <v>0.46</v>
+      </c>
+      <c r="G19">
+        <v>0.6453</v>
       </c>
     </row>
     <row r="20">
@@ -838,19 +878,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>6.260760251136052E+27</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>6.260760251136052E+27</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>6.260760251136052E+27</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F20">
-        <v>3.080064573983932E+21</v>
+        <v>-4.034</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="21">
@@ -865,19 +905,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>1702.695</v>
+        <v>0.111</v>
       </c>
       <c r="D21">
-        <v>1514.189</v>
+        <v>0.006</v>
       </c>
       <c r="E21">
-        <v>1914.669</v>
+        <v>2.199</v>
       </c>
       <c r="F21">
-        <v>124.282</v>
+        <v>-1.443</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="22">
@@ -892,16 +932,16 @@
         </is>
       </c>
       <c r="C22">
-        <v>4.482229763467052E+115</v>
+        <v>151134144.697</v>
       </c>
       <c r="D22">
-        <v>4.482229763467052E+115</v>
+        <v>104182684.484</v>
       </c>
       <c r="E22">
-        <v>4.482229763467052E+115</v>
+        <v>219244971.527</v>
       </c>
       <c r="F22">
-        <v>1.617268554771498E+22</v>
+        <v>99.22499999999999</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -921,6 +961,18 @@
       <c r="C23">
         <v>0</v>
       </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>-1933706.782</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -943,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>-1.367856528257976E+21</v>
+        <v>-3561.762</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -970,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>-272.354</v>
+        <v>-8.112</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -990,6 +1042,18 @@
       <c r="C26">
         <v>0</v>
       </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>-6.649</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1012,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>-3611406594.171</v>
+        <v>-4.343</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1030,19 +1094,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>2863664113.575</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D28">
-        <v>2742516682.575</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>2990163089.064</v>
+        <v>16257.479</v>
       </c>
       <c r="F28">
-        <v>987.3630000000001</v>
+        <v>-0.642</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>0.5211</v>
       </c>
     </row>
     <row r="29">
@@ -1059,6 +1123,18 @@
       <c r="C29">
         <v>0</v>
       </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>-8.108000000000001</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1081,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>-3796452102942268</v>
+        <v>-448161519847.797</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -1099,19 +1175,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>7197.355</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>0.338</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>153097281.013</v>
       </c>
       <c r="F31">
-        <v>-488716304.294</v>
+        <v>1.747</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>0.08069999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1126,16 +1202,16 @@
         </is>
       </c>
       <c r="C32">
-        <v>6.482927878203427E+93</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>6.208667341125028E+93</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>6.769303550151479E+93</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>9794.547</v>
+        <v>-4.991</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1149,20 +1225,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>`p3_agregado_Población afrodescendiente`</t>
+          <t>`p7_agregado_Desocupado o inactivo`</t>
         </is>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>9579588441.246</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>7428317.474</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>12353876234002.3</v>
       </c>
       <c r="F33">
-        <v>-8404716242.102</v>
+        <v>6.29</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -1176,13 +1252,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>`p3_agregado_Pueblos indígenas`</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>151701000119118.3</v>
+      </c>
+      <c r="D34">
+        <v>14471016884.157</v>
+      </c>
+      <c r="E34">
+        <v>1.590295528045128E+18</v>
+      </c>
+      <c r="F34">
+        <v>6.913</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1193,11 +1279,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>`p3_agregado_Sin respuesta`</t>
+          <t>educacion_Secundaria</t>
         </is>
       </c>
       <c r="C35">
         <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>1082.049</v>
+      </c>
+      <c r="F35">
+        <v>-1.197</v>
+      </c>
+      <c r="G35">
+        <v>0.2311</v>
       </c>
     </row>
     <row r="36">
@@ -1208,23 +1306,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>`p5_agregado_Primaria o menos`</t>
+          <t>p1edad</t>
         </is>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>0.457</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>27.034</v>
       </c>
       <c r="F36">
-        <v>-1583.236</v>
+        <v>-0.376</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>0.7068</v>
       </c>
     </row>
     <row r="37">
@@ -1235,10 +1333,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>`p5_agregado_Técnico / Tecnológico`</t>
+          <t>p23_agregado_Estudio</t>
         </is>
       </c>
       <c r="C37">
+        <v>515769.386</v>
+      </c>
+      <c r="D37">
+        <v>506396.905</v>
+      </c>
+      <c r="E37">
+        <v>525315.334</v>
+      </c>
+      <c r="F37">
+        <v>1405.787</v>
+      </c>
+      <c r="G37">
         <v>0</v>
       </c>
     </row>
@@ -1250,11 +1360,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>`p7_agregado_Desocupado o inactivo`</t>
+          <t>p24</t>
         </is>
       </c>
       <c r="C38">
-        <v>1.086047698480961E+39</v>
+        <v>4.301</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>1629792966051.487</v>
+      </c>
+      <c r="F38">
+        <v>0.107</v>
+      </c>
+      <c r="G38">
+        <v>0.9146</v>
       </c>
     </row>
     <row r="39">
@@ -1265,23 +1387,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
+          <t>p28_importancia_comodidad</t>
         </is>
       </c>
       <c r="C39">
-        <v>2.468626841919825E+181</v>
+        <v>0.004</v>
       </c>
       <c r="D39">
-        <v>2.364191479080909E+181</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>2.577675513413223E+181</v>
+        <v>77488806.009</v>
       </c>
       <c r="F39">
-        <v>18938.53</v>
+        <v>-0.45</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="40">
@@ -1292,23 +1414,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>p1edad</t>
+          <t>p28_importancia_costo_compra</t>
         </is>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>135.694</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>4.284425966826964E+69</v>
+        <v>19323720554333.14</v>
       </c>
       <c r="F40">
-        <v>-0.112</v>
+        <v>0.375</v>
       </c>
       <c r="G40">
-        <v>0.9111</v>
+        <v>0.7078</v>
       </c>
     </row>
     <row r="41">
@@ -1319,23 +1441,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>p23_agregado_Estudio</t>
+          <t>p28_importancia_costo_uso</t>
         </is>
       </c>
       <c r="C41">
-        <v>5.870828869482544E+89</v>
+        <v>0.001</v>
       </c>
       <c r="D41">
-        <v>5.870828869480541E+89</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>5.870828869484545E+89</v>
+        <v>59361718.029</v>
       </c>
       <c r="F41">
-        <v>1156293866594706</v>
+        <v>-0.547</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>0.5846</v>
       </c>
     </row>
     <row r="42">
@@ -1346,7 +1468,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>p24</t>
+          <t>p28_importancia_discriminacion</t>
         </is>
       </c>
       <c r="C42">
@@ -1356,13 +1478,13 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>4733338.214</v>
       </c>
       <c r="F42">
-        <v>-9.173</v>
+        <v>-0.695</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>0.4873</v>
       </c>
     </row>
     <row r="43">
@@ -1373,23 +1495,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>p28_importancia_comodidad</t>
+          <t>p28_importancia_emisiones</t>
         </is>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>144682.04</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>27496499905181.65</v>
       </c>
       <c r="F43">
-        <v>-16.296</v>
+        <v>1.222</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>0.2218</v>
       </c>
     </row>
     <row r="44">
@@ -1400,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>p28_importancia_costo_compra</t>
+          <t>p28_importancia_riesgo_acoso</t>
         </is>
       </c>
       <c r="C44">
-        <v>1381786092.91</v>
+        <v>0.045</v>
       </c>
       <c r="D44">
-        <v>10491727.082</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>181984604783.796</v>
+        <v>2579702418.889</v>
       </c>
       <c r="F44">
-        <v>8.452</v>
+        <v>-0.245</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>0.8061</v>
       </c>
     </row>
     <row r="45">
@@ -1427,23 +1549,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>p28_importancia_costo_uso</t>
+          <t>p28_importancia_riesgo_robo</t>
         </is>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>2735823.156</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>1240963582077123</v>
       </c>
       <c r="F45">
-        <v>-5.31</v>
+        <v>1.457</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="46">
@@ -1454,7 +1576,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>p28_importancia_discriminacion</t>
+          <t>p28_importancia_siniestralidad</t>
         </is>
       </c>
       <c r="C46">
@@ -1464,13 +1586,13 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>66.815</v>
       </c>
       <c r="F46">
-        <v>-96.672</v>
+        <v>-1.472</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="47">
@@ -1481,23 +1603,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>p28_importancia_emisiones</t>
+          <t>p28_importancia_tiempo</t>
         </is>
       </c>
       <c r="C47">
-        <v>6.179308370837537E+147</v>
+        <v>12.65</v>
       </c>
       <c r="D47">
-        <v>7.501901453375331E+145</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>5.089889833826435E+149</v>
+        <v>14711586032.795</v>
       </c>
       <c r="F47">
-        <v>151.203</v>
+        <v>0.238</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>0.8117</v>
       </c>
     </row>
     <row r="48">
@@ -1508,23 +1630,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>p28_importancia_riesgo_acoso</t>
+          <t>p32_contaminacion_likert</t>
         </is>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1559161566.739</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>154.853</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1.569867204342954E+16</v>
       </c>
       <c r="F48">
-        <v>-17.219</v>
+        <v>2.573</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>0.0101</v>
       </c>
     </row>
     <row r="49">
@@ -1535,23 +1657,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>p28_importancia_riesgo_robo</t>
+          <t>p38p38_dummy_1</t>
         </is>
       </c>
       <c r="C49">
-        <v>2.138566688511446E+95</v>
+        <v>437131.434</v>
       </c>
       <c r="D49">
-        <v>7.449762698798564E+89</v>
+        <v>10.706</v>
       </c>
       <c r="E49">
-        <v>6.139078070162399E+100</v>
+        <v>17848019422.488</v>
       </c>
       <c r="F49">
-        <v>34.234</v>
+        <v>2.398</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>0.0165</v>
       </c>
     </row>
     <row r="50">
@@ -1562,23 +1684,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>p28_importancia_siniestralidad</t>
+          <t>p3_minoria_Sí</t>
         </is>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>123.065</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>165809.86</v>
       </c>
       <c r="F50">
-        <v>-24.382</v>
+        <v>1.309</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>0.1905</v>
       </c>
     </row>
     <row r="51">
@@ -1589,23 +1711,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>p28_importancia_tiempo</t>
+          <t>p40_Mujer</t>
         </is>
       </c>
       <c r="C51">
-        <v>2.098284978353452E+46</v>
+        <v>8886.603999999999</v>
       </c>
       <c r="D51">
-        <v>1.311730424715002E+37</v>
+        <v>3.882</v>
       </c>
       <c r="E51">
-        <v>3.356482221825676E+55</v>
+        <v>20345119.34</v>
       </c>
       <c r="F51">
-        <v>9.864000000000001</v>
+        <v>2.304</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>0.0212</v>
       </c>
     </row>
     <row r="52">
@@ -1616,20 +1738,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>p32_contaminacion_likert</t>
+          <t>p7_agregado_Estudiante</t>
         </is>
       </c>
       <c r="C52">
-        <v>4.713323760296749E+96</v>
+        <v>5.009531298099098E+17</v>
       </c>
       <c r="D52">
-        <v>1.477934549208105E+91</v>
+        <v>4.930227726463188E+17</v>
       </c>
       <c r="E52">
-        <v>1.503139694601575E+102</v>
+        <v>5.0901104814964E+17</v>
       </c>
       <c r="F52">
-        <v>34.428</v>
+        <v>5005.92</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -1643,20 +1765,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>p36_influencia_amigos</t>
+          <t>p9_estrato3_Bajo</t>
         </is>
       </c>
       <c r="C53">
-        <v>4.886950918866695E+107</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>3.710595730566433E+105</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>6.436241244681844E+109</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>99.581</v>
+        <v>-5.94</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -1670,7 +1792,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>p37_influencia_familia</t>
+          <t>p9_estrato3_Medio</t>
         </is>
       </c>
       <c r="C54">
@@ -1683,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="F54">
-        <v>-57.519</v>
+        <v>-5.486</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -1697,47 +1819,47 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>p38p38_dummy_1</t>
+          <t>tiempo_total</t>
         </is>
       </c>
       <c r="C55">
-        <v>1.35217578588388E+87</v>
+        <v>0.767</v>
       </c>
       <c r="D55">
-        <v>1.151660221277252E+87</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E55">
-        <v>1.587603116050078E+87</v>
+        <v>7.018</v>
       </c>
       <c r="F55">
-        <v>2449.861</v>
+        <v>-0.235</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>0.8143</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Auto privado</t>
+          <t>Modo activo</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>p40_Mujer</t>
+          <t>(Intercept)</t>
         </is>
       </c>
       <c r="C56">
-        <v>9.965941896830818E+80</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>9.544332308023504E+80</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>1.040617559046156E+81</v>
+        <v>0</v>
       </c>
       <c r="F56">
-        <v>8456.762000000001</v>
+        <v>-8.59</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -1746,12 +1868,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Auto privado</t>
+          <t>Modo activo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>p5_agregado_Secundaria</t>
+          <t>`edad_r2_18 - 34 años`</t>
         </is>
       </c>
       <c r="C57">
@@ -1761,52 +1883,64 @@
         <v>0</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>207584.699</v>
       </c>
       <c r="F57">
-        <v>-23493.728</v>
+        <v>-0.794</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>0.4274</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Auto privado</t>
+          <t>Modo activo</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>p7_agregado_Estudiante</t>
+          <t>`edad_r2_55 - 80 años`</t>
         </is>
       </c>
       <c r="C58">
-        <v>2.248760080357771E+141</v>
+        <v>3.079560961502148E+29</v>
+      </c>
+      <c r="D58">
+        <v>1.584552176130924E+25</v>
+      </c>
+      <c r="E58">
+        <v>5.985095258121963E+33</v>
+      </c>
+      <c r="F58">
+        <v>13.477</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Auto privado</t>
+          <t>Modo activo</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>p9_estrato3_Bajo</t>
+          <t>`educacion_Primaria o menos`</t>
         </is>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>9.892661257153154E+32</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>4.273866666141756E+26</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>2.28984089569475E+39</v>
       </c>
       <c r="F59">
-        <v>-2238251325555.365</v>
+        <v>10.161</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -1815,55 +1949,55 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Auto privado</t>
+          <t>Modo activo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>p9_estrato3_Medio</t>
+          <t>`p15_autos_agregado_1 auto`</t>
         </is>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>370275621.123</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>1.812998964220921E+18</v>
       </c>
       <c r="F60">
-        <v>-7208.181</v>
+        <v>1.733</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>0.08309999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Auto privado</t>
+          <t>Modo activo</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>tiempo_total</t>
+          <t>`p15_autos_agregado_2 o más autos`</t>
         </is>
       </c>
       <c r="C61">
-        <v>8551.587</v>
+        <v>0</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>1.881298939634446E+86</v>
+        <v>0</v>
       </c>
       <c r="F61">
-        <v>0.094</v>
+        <v>-163530.583</v>
       </c>
       <c r="G61">
-        <v>0.9254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1874,20 +2008,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>(Intercept)</t>
+          <t>`p16_motos_agregado_1 motocicleta`</t>
         </is>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>9.669189258174291E+36</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1.055673756292579E+31</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>8.856260786356193E+42</v>
       </c>
       <c r="F62">
-        <v>-235.95</v>
+        <v>12.159</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -1901,20 +2035,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>`edad_r2_18 - 34 años`</t>
+          <t>`p16_motos_agregado_Sin motocicletas`</t>
         </is>
       </c>
       <c r="C63">
-        <v>4.687138715965342E+37</v>
+        <v>7.141467595823132E+45</v>
       </c>
       <c r="D63">
-        <v>1.046828755104761E+35</v>
+        <v>1.830355865562387E+37</v>
       </c>
       <c r="E63">
-        <v>2.098649777775992E+40</v>
+        <v>2.786373971409195E+54</v>
       </c>
       <c r="F63">
-        <v>27.851</v>
+        <v>10.461</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -1928,26 +2062,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>`edad_r2_55 - 80 años`</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>`p19comuna_Comuna 1 - Popular`</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
       </c>
       <c r="F64">
-        <v>470.017</v>
+        <v>-5.407</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -1961,20 +2089,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>`p12_dificultad_binaria_Con alguna dificultad`</t>
+          <t>`p19comuna_Comuna 10 - La Candelaria`</t>
         </is>
       </c>
       <c r="C65">
-        <v>2.066976994146423E+219</v>
+        <v>9.34219247026471E+17</v>
       </c>
       <c r="D65">
-        <v>2.060100836370999E+219</v>
+        <v>96644460536.929</v>
       </c>
       <c r="E65">
-        <v>2.073876103005075E+219</v>
+        <v>9.030684186821167E+24</v>
       </c>
       <c r="F65">
-        <v>297034.701</v>
+        <v>5.042</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -1988,23 +2116,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_1 auto`</t>
+          <t>`p19comuna_Comuna 11 - Laureles Estadio`</t>
         </is>
       </c>
       <c r="C66">
-        <v>1.011451759861834E+73</v>
+        <v>0.406</v>
       </c>
       <c r="D66">
-        <v>2.074367994645426E+71</v>
+        <v>0.048</v>
       </c>
       <c r="E66">
-        <v>4.931789659155774E+74</v>
+        <v>3.414</v>
       </c>
       <c r="F66">
-        <v>84.76600000000001</v>
+        <v>-0.83</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>0.4066</v>
       </c>
     </row>
     <row r="67">
@@ -2015,23 +2143,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_2 o más autos`</t>
+          <t>`p19comuna_Comuna 12 - La América`</t>
         </is>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>15.613</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>2737248959.662</v>
       </c>
       <c r="F67">
-        <v>-4.471503862193015E+62</v>
+        <v>0.284</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>0.7766</v>
       </c>
     </row>
     <row r="68">
@@ -2042,26 +2170,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_1 motocicleta`</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>`p19comuna_Comuna 13 - San Javier`</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>384483.99</v>
+        <v>-57581.661</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -2075,29 +2197,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_Sin motocicletas`</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>`p19comuna_Comuna 14 - El Poblado`</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>29.166</v>
       </c>
       <c r="F69">
-        <v>1206.387</v>
+        <v>-1.55</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>0.1212</v>
       </c>
     </row>
     <row r="70">
@@ -2108,23 +2224,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 1 - Popular`</t>
+          <t>`p19comuna_Comuna 15 - Guayabal`</t>
         </is>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>22.129</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>73873668295.87</v>
       </c>
       <c r="F70">
-        <v>-2.063198378509788E+32</v>
+        <v>0.277</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>0.7819</v>
       </c>
     </row>
     <row r="71">
@@ -2135,26 +2251,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 10 - La Candelaria`</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>`p19comuna_Comuna 2 - Santa Cruz`</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>2.427095457605368E+28</v>
+        <v>-15.65</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -2168,7 +2278,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 11 - Laureles Estadio`</t>
+          <t>`p19comuna_Comuna 3 - Manrique`</t>
         </is>
       </c>
       <c r="C72">
@@ -2181,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="F72">
-        <v>-9.411664008103961E+19</v>
+        <v>-4.894</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -2195,7 +2305,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 12 - La América`</t>
+          <t>`p19comuna_Comuna 4 - Aranjuez`</t>
         </is>
       </c>
       <c r="C73">
@@ -2208,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="F73">
-        <v>-3.046707427088507E+39</v>
+        <v>-26.447</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -2222,22 +2332,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 13 - San Javier`</t>
+          <t>`p19comuna_Comuna 5 - Castilla`</t>
         </is>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>42949227.726</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>42738686.281</v>
       </c>
       <c r="E74">
-        <v>0</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
+        <v>43160806.351</v>
+      </c>
+      <c r="F74">
+        <v>7009.961</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -2251,7 +2359,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 14 - El Poblado`</t>
+          <t>`p19comuna_Comuna 6 - Doce de Octubre`</t>
         </is>
       </c>
       <c r="C75">
@@ -2264,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="F75">
-        <v>-16009.34</v>
+        <v>-4.692</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -2278,7 +2386,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 15 - Guayabal`</t>
+          <t>`p19comuna_Comuna 7 - Robledo`</t>
         </is>
       </c>
       <c r="C76">
@@ -2291,10 +2399,10 @@
         <v>0</v>
       </c>
       <c r="F76">
-        <v>-15444038246.972</v>
+        <v>-3.174</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="77">
@@ -2305,7 +2413,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 2 - Santa Cruz`</t>
+          <t>`p19comuna_Comuna 8 - Villa Hermosa`</t>
         </is>
       </c>
       <c r="C77">
@@ -2315,15 +2423,13 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>0</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
+        <v>342986.406</v>
+      </c>
+      <c r="F77">
+        <v>-0.84</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>0.4011</v>
       </c>
     </row>
     <row r="78">
@@ -2334,23 +2440,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 3 - Manrique`</t>
+          <t>`p19comuna_Comuna 9 - Buenos Aires`</t>
         </is>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>6326100465899.889</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>93332.867</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>4.287830043596155E+20</v>
       </c>
       <c r="F78">
-        <v>-107635.117</v>
+        <v>3.204</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="79">
@@ -2361,23 +2467,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 4 - Aranjuez`</t>
+          <t>`p22_Entre 11 y 15 km`</t>
         </is>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>23.343</v>
       </c>
       <c r="F79">
-        <v>-1.464359561316009E+44</v>
+        <v>-1.373</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>0.1698</v>
       </c>
     </row>
     <row r="80">
@@ -2388,20 +2494,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 5 - Castilla`</t>
+          <t>`p22_Entre 16 y 20 km`</t>
         </is>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>3.55152218596461E+31</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>1.626605093708822E+25</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>7.754377436897875E+37</v>
       </c>
       <c r="F80">
-        <v>-1.696501129714676E+28</v>
+        <v>9.755000000000001</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -2415,23 +2521,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 6 - Doce de Octubre`</t>
+          <t>`p22_Entre 6 y 10 km`</t>
         </is>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>1.126619135158017E+19</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>96067391.19599999</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>1.321229461839924E+30</v>
       </c>
       <c r="F81">
-        <v>-3284.409</v>
+        <v>3.373</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="82">
@@ -2442,20 +2548,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 7 - Robledo`</t>
+          <t>`p22_Menos de 5 km`</t>
         </is>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>1.088591136435389E+31</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>2.777991097192925E+23</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>4.265782793627814E+38</v>
       </c>
       <c r="F82">
-        <v>-32459349.964</v>
+        <v>8.010999999999999</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -2469,23 +2575,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 8 - Villa Hermosa`</t>
+          <t>`p23_agregado_Compras y trámites`</t>
         </is>
       </c>
       <c r="C83">
-        <v>7.991616138532294E+22</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>1.806945174278141E+22</v>
+        <v>0</v>
       </c>
       <c r="E83">
-        <v>3.534469634982905E+23</v>
+        <v>10.512</v>
       </c>
       <c r="F83">
-        <v>69.521</v>
+        <v>-1.726</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>0.0843</v>
       </c>
     </row>
     <row r="84">
@@ -2496,26 +2602,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 9 - Buenos Aires`</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>`p23_agregado_Cuidado y familia`</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
       </c>
       <c r="F84">
-        <v>528.921</v>
+        <v>-6.578</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -2529,20 +2629,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>`p22_Entre 11 y 15 km`</t>
+          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
         </is>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>91503808494684.66</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>44538282.314</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>1.879943844695669E+20</v>
       </c>
       <c r="F85">
-        <v>-5103887315651.548</v>
+        <v>4.335</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -2556,26 +2656,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>`p22_Entre 16 y 20 km`</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>`p23_agregado_Visitas sociales`</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
       </c>
       <c r="F86">
-        <v>710.057</v>
+        <v>-31.244</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -2589,23 +2683,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>`p22_Entre 6 y 10 km`</t>
+          <t>`p7_agregado_Desocupado o inactivo`</t>
         </is>
       </c>
       <c r="C87">
-        <v>5.545193676232433E+218</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>1.238487793962976E+216</v>
+        <v>0</v>
       </c>
       <c r="E87">
-        <v>2.48279983515505E+221</v>
+        <v>5786.514</v>
       </c>
       <c r="F87">
-        <v>161.725</v>
+        <v>-1.04</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>0.2985</v>
       </c>
     </row>
     <row r="88">
@@ -2616,29 +2710,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>`p22_Menos de 5 km`</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>8640.074000000001</v>
+      </c>
+      <c r="D88">
+        <v>0.249</v>
+      </c>
+      <c r="E88">
+        <v>299436010.524</v>
       </c>
       <c r="F88">
-        <v>1245.755</v>
+        <v>1.7</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>0.0892</v>
       </c>
     </row>
     <row r="89">
@@ -2649,23 +2737,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>`p23_agregado_Compras y trámites`</t>
+          <t>educacion_Secundaria</t>
         </is>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>8339.186</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>449154379964.401</v>
       </c>
       <c r="F89">
-        <v>-123764.567</v>
+        <v>0.994</v>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>0.3202</v>
       </c>
     </row>
     <row r="90">
@@ -2676,23 +2764,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>`p23_agregado_Cuidado y familia`</t>
+          <t>p1edad</t>
         </is>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>0.663</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>0.264</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>1.665</v>
       </c>
       <c r="F90">
-        <v>-1.775684146857139E+155</v>
+        <v>-0.874</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>0.3822</v>
       </c>
     </row>
     <row r="91">
@@ -2703,23 +2791,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
+          <t>p23_agregado_Estudio</t>
         </is>
       </c>
       <c r="C91">
-        <v>2.348082739930422E+94</v>
+        <v>199210940.411</v>
       </c>
       <c r="D91">
-        <v>4.809638236901567E+92</v>
+        <v>6.173</v>
       </c>
       <c r="E91">
-        <v>1.146342465272611E+96</v>
+        <v>6428790652512880</v>
       </c>
       <c r="F91">
-        <v>109.538</v>
+        <v>2.166</v>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>0.0303</v>
       </c>
     </row>
     <row r="92">
@@ -2730,7 +2818,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>`p23_agregado_Visitas sociales`</t>
+          <t>p24</t>
         </is>
       </c>
       <c r="C92">
@@ -2740,13 +2828,13 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="F92">
-        <v>-1.033156607998378E+54</v>
+        <v>-2.976</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>0.0029</v>
       </c>
     </row>
     <row r="93">
@@ -2757,11 +2845,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>`p3_agregado_Población afrodescendiente`</t>
+          <t>p28_importancia_comodidad</t>
         </is>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>0.007</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>111229.992</v>
+      </c>
+      <c r="F93">
+        <v>-0.589</v>
+      </c>
+      <c r="G93">
+        <v>0.556</v>
       </c>
     </row>
     <row r="94">
@@ -2772,23 +2872,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>`p3_agregado_Pueblos indígenas`</t>
+          <t>p28_importancia_costo_compra</t>
         </is>
       </c>
       <c r="C94">
-        <v>1.931391525612226E+239</v>
+        <v>689250.6629999999</v>
       </c>
       <c r="D94">
-        <v>1.931391525612226E+239</v>
+        <v>21.418</v>
       </c>
       <c r="E94">
-        <v>1.931391525612226E+239</v>
+        <v>22180879452.862</v>
       </c>
       <c r="F94">
-        <v>4.323945122988452E+146</v>
+        <v>2.539</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>0.0111</v>
       </c>
     </row>
     <row r="95">
@@ -2799,23 +2899,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>`p3_agregado_Sin respuesta`</t>
+          <t>p28_importancia_costo_uso</t>
         </is>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>13.894</v>
       </c>
       <c r="F95">
-        <v>-2.219847106439959E+29</v>
+        <v>-1.355</v>
       </c>
       <c r="G95">
-        <v>0</v>
+        <v>0.1754</v>
       </c>
     </row>
     <row r="96">
@@ -2826,29 +2926,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>`p5_agregado_Primaria o menos`</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>p28_importancia_discriminacion</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>1.181</v>
       </c>
       <c r="F96">
-        <v>6289.214</v>
+        <v>-1.93</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>0.0536</v>
       </c>
     </row>
     <row r="97">
@@ -2859,23 +2953,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>`p5_agregado_Técnico / Tecnológico`</t>
+          <t>p28_importancia_emisiones</t>
         </is>
       </c>
       <c r="C97">
-        <v>6.979361230789776E+59</v>
+        <v>512297425.902</v>
       </c>
       <c r="D97">
-        <v>1.558775297198317E+57</v>
+        <v>158.978</v>
       </c>
       <c r="E97">
-        <v>3.124984292309708E+62</v>
+        <v>1650844385251277</v>
       </c>
       <c r="F97">
-        <v>44.245</v>
+        <v>2.623</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>0.008699999999999999</v>
       </c>
     </row>
     <row r="98">
@@ -2886,23 +2980,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>`p7_agregado_Desocupado o inactivo`</t>
+          <t>p28_importancia_riesgo_acoso</t>
         </is>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>1.826</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>214276.401</v>
       </c>
       <c r="F98">
-        <v>-61681.247</v>
+        <v>0.101</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>0.9195</v>
       </c>
     </row>
     <row r="99">
@@ -2913,23 +3007,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
+          <t>p28_importancia_riesgo_robo</t>
         </is>
       </c>
       <c r="C99">
-        <v>6.549140420270326E+148</v>
+        <v>548.955</v>
       </c>
       <c r="D99">
-        <v>1.341477267751818E+147</v>
+        <v>0</v>
       </c>
       <c r="E99">
-        <v>3.197313981794117E+150</v>
+        <v>2784560592.944</v>
       </c>
       <c r="F99">
-        <v>172.735</v>
+        <v>0.801</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>0.4233</v>
       </c>
     </row>
     <row r="100">
@@ -2940,7 +3034,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>p1edad</t>
+          <t>p28_importancia_siniestralidad</t>
         </is>
       </c>
       <c r="C100">
@@ -2950,13 +3044,13 @@
         <v>0</v>
       </c>
       <c r="E100">
-        <v>13216745625.847</v>
+        <v>0.001</v>
       </c>
       <c r="F100">
-        <v>-0.525</v>
+        <v>-3.146</v>
       </c>
       <c r="G100">
-        <v>0.5994</v>
+        <v>0.0017</v>
       </c>
     </row>
     <row r="101">
@@ -2967,23 +3061,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>p23_agregado_Estudio</t>
+          <t>p28_importancia_tiempo</t>
         </is>
       </c>
       <c r="C101">
-        <v>86265.689</v>
+        <v>0.036</v>
       </c>
       <c r="D101">
-        <v>86265.689</v>
+        <v>0</v>
       </c>
       <c r="E101">
-        <v>86265.689</v>
+        <v>30973.229</v>
       </c>
       <c r="F101">
-        <v>2.445834450733137E+23</v>
+        <v>-0.477</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>0.6337</v>
       </c>
     </row>
     <row r="102">
@@ -2994,7 +3088,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>p24</t>
+          <t>p32_contaminacion_likert</t>
         </is>
       </c>
       <c r="C102">
@@ -3004,13 +3098,13 @@
         <v>0</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="F102">
-        <v>-39.828</v>
+        <v>-2.764</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="103">
@@ -3021,20 +3115,20 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>p28_importancia_comodidad</t>
+          <t>p38p38_dummy_1</t>
         </is>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>7.355816606408942E+22</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>1723473323653595</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>3.139476382054921E+30</v>
       </c>
       <c r="F103">
-        <v>-39.752</v>
+        <v>5.874</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -3048,23 +3142,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>p28_importancia_costo_compra</t>
+          <t>p3_minoria_Sí</t>
         </is>
       </c>
       <c r="C104">
-        <v>3.448437409877037E+50</v>
+        <v>178.328</v>
       </c>
       <c r="D104">
-        <v>1.470055896430643E+43</v>
+        <v>0</v>
       </c>
       <c r="E104">
-        <v>8.089298236014843E+57</v>
+        <v>165290144879.645</v>
       </c>
       <c r="F104">
-        <v>13.44</v>
+        <v>0.492</v>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>0.6227</v>
       </c>
     </row>
     <row r="105">
@@ -3075,7 +3169,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>p28_importancia_costo_uso</t>
+          <t>p40_Mujer</t>
         </is>
       </c>
       <c r="C105">
@@ -3085,13 +3179,13 @@
         <v>0</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>3.626</v>
       </c>
       <c r="F105">
-        <v>-16.904</v>
+        <v>-1.847</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>0.0648</v>
       </c>
     </row>
     <row r="106">
@@ -3102,23 +3196,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>p28_importancia_discriminacion</t>
+          <t>p7_agregado_Estudiante</t>
         </is>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>1.480621618042722E+31</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>2.02927575311921E+25</v>
       </c>
       <c r="E106">
-        <v>0.008999999999999999</v>
+        <v>1.080306790462424E+37</v>
       </c>
       <c r="F106">
-        <v>-2.419</v>
+        <v>10.42</v>
       </c>
       <c r="G106">
-        <v>0.0155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -3129,20 +3223,20 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>p28_importancia_emisiones</t>
+          <t>p9_estrato3_Bajo</t>
         </is>
       </c>
       <c r="C107">
-        <v>3.565030097590247E+121</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>6.578909790518023E+118</v>
+        <v>0</v>
       </c>
       <c r="E107">
-        <v>1.931845853098951E+124</v>
+        <v>0</v>
       </c>
       <c r="F107">
-        <v>87.143</v>
+        <v>-5.167</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -3156,7 +3250,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>p28_importancia_riesgo_acoso</t>
+          <t>p9_estrato3_Medio</t>
         </is>
       </c>
       <c r="C108">
@@ -3169,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="F108">
-        <v>-4.378</v>
+        <v>-6.242</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -3183,34 +3277,34 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>p28_importancia_riesgo_robo</t>
+          <t>tiempo_total</t>
         </is>
       </c>
       <c r="C109">
-        <v>2.546588705862434E+38</v>
+        <v>2.132</v>
       </c>
       <c r="D109">
-        <v>7.823104232787713E+29</v>
+        <v>0.954</v>
       </c>
       <c r="E109">
-        <v>8.289694018962571E+46</v>
+        <v>4.762</v>
       </c>
       <c r="F109">
-        <v>8.843</v>
+        <v>1.846</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>0.0649</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>p28_importancia_siniestralidad</t>
+          <t>(Intercept)</t>
         </is>
       </c>
       <c r="C110">
@@ -3223,34 +3317,34 @@
         <v>0</v>
       </c>
       <c r="F110">
-        <v>-76.831</v>
+        <v>-3.85</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>p28_importancia_tiempo</t>
+          <t>`edad_r2_18 - 34 años`</t>
         </is>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>3.794926233397736E+17</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>225324854594.395</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>6.391423237731251E+23</v>
       </c>
       <c r="F111">
-        <v>-4.558</v>
+        <v>5.534</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -3259,12 +3353,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>p32_contaminacion_likert</t>
+          <t>`edad_r2_55 - 80 años`</t>
         </is>
       </c>
       <c r="C112">
@@ -3274,37 +3368,37 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>253.374</v>
       </c>
       <c r="F112">
-        <v>-479.454</v>
+        <v>-1.297</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>0.1945</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>p36_influencia_amigos</t>
+          <t>`educacion_Primaria o menos`</t>
         </is>
       </c>
       <c r="C113">
-        <v>4.528074653279279E+96</v>
+        <v>42830198902.546</v>
       </c>
       <c r="D113">
-        <v>1.770785820192543E+95</v>
+        <v>346819.027</v>
       </c>
       <c r="E113">
-        <v>1.157873517613827E+98</v>
+        <v>5289288632183332</v>
       </c>
       <c r="F113">
-        <v>134.574</v>
+        <v>4.093</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -3313,66 +3407,66 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>p37_influencia_familia</t>
+          <t>`p15_autos_agregado_1 auto`</t>
         </is>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>2416703.296</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>5.815</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>1004434309548.259</v>
       </c>
       <c r="F114">
-        <v>-135.634</v>
+        <v>2.227</v>
       </c>
       <c r="G114">
-        <v>0</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>p38p38_dummy_1</t>
+          <t>`p15_autos_agregado_2 o más autos`</t>
         </is>
       </c>
       <c r="C115">
-        <v>3.486253509250816E+183</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>1.043427983951256E+182</v>
+        <v>0</v>
       </c>
       <c r="E115">
-        <v>1.164810961340999E+185</v>
+        <v>0.546</v>
       </c>
       <c r="F115">
-        <v>236.068</v>
+        <v>-2.02</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>0.0434</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>p40_Mujer</t>
+          <t>`p16_motos_agregado_1 motocicleta`</t>
         </is>
       </c>
       <c r="C116">
@@ -3382,37 +3476,37 @@
         <v>0</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F116">
-        <v>-128.847</v>
+        <v>-3.154</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>p5_agregado_Secundaria</t>
+          <t>`p16_motos_agregado_Sin motocicletas`</t>
         </is>
       </c>
       <c r="C117">
-        <v>2.05368847091556E+123</v>
+        <v>2.988603569197029E+20</v>
       </c>
       <c r="D117">
-        <v>4.209539408412258E+121</v>
+        <v>1.457945033001256E+16</v>
       </c>
       <c r="E117">
-        <v>1.001923471043662E+125</v>
+        <v>6.126260655678316E+24</v>
       </c>
       <c r="F117">
-        <v>143.157</v>
+        <v>9.308</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -3421,31 +3515,25 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>p7_agregado_Estudiante</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>`p19comuna_Comuna 1 - Popular`</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
       </c>
       <c r="F118">
-        <v>1.165339673667413E+18</v>
+        <v>-8.898999999999999</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -3454,12 +3542,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>p9_estrato3_Bajo</t>
+          <t>`p19comuna_Comuna 10 - La Candelaria`</t>
         </is>
       </c>
       <c r="C119">
@@ -3472,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="F119">
-        <v>-520.653</v>
+        <v>-4.376</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -3481,12 +3569,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>p9_estrato3_Medio</t>
+          <t>`p19comuna_Comuna 11 - Laureles Estadio`</t>
         </is>
       </c>
       <c r="C120">
@@ -3496,40 +3584,40 @@
         <v>0</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>1224.671</v>
       </c>
       <c r="F120">
-        <v>-915.643</v>
+        <v>-1.274</v>
       </c>
       <c r="G120">
-        <v>0</v>
+        <v>0.2026</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>tiempo_total</t>
+          <t>`p19comuna_Comuna 12 - La América`</t>
         </is>
       </c>
       <c r="C121">
-        <v>1663754.105</v>
+        <v>9.204908846176271E+27</v>
       </c>
       <c r="D121">
-        <v>0.467</v>
+        <v>6.435945185913669E+21</v>
       </c>
       <c r="E121">
-        <v>5924359338047.97</v>
+        <v>1.316517534236668E+34</v>
       </c>
       <c r="F121">
-        <v>1.861</v>
+        <v>8.904</v>
       </c>
       <c r="G121">
-        <v>0.06270000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3540,7 +3628,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>(Intercept)</t>
+          <t>`p19comuna_Comuna 13 - San Javier`</t>
         </is>
       </c>
       <c r="C122">
@@ -3553,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="F122">
-        <v>-195.462</v>
+        <v>-14.722</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -3567,23 +3655,23 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>`edad_r2_18 - 34 años`</t>
+          <t>`p19comuna_Comuna 14 - El Poblado`</t>
         </is>
       </c>
       <c r="C123">
-        <v>1.992197350882711E+267</v>
+        <v>172793359.901</v>
       </c>
       <c r="D123">
-        <v>1.301028519942338E+250</v>
+        <v>19.804</v>
       </c>
       <c r="E123">
-        <v>3.050548257804518E+284</v>
+        <v>1507683249375467</v>
       </c>
       <c r="F123">
-        <v>30.486</v>
+        <v>2.326</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="124">
@@ -3594,7 +3682,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>`edad_r2_55 - 80 años`</t>
+          <t>`p19comuna_Comuna 15 - Guayabal`</t>
         </is>
       </c>
       <c r="C124">
@@ -3604,13 +3692,13 @@
         <v>0</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F124">
-        <v>-27.605</v>
+        <v>-2.553</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>0.0107</v>
       </c>
     </row>
     <row r="125">
@@ -3621,23 +3709,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>`p12_dificultad_binaria_Con alguna dificultad`</t>
+          <t>`p19comuna_Comuna 2 - Santa Cruz`</t>
         </is>
       </c>
       <c r="C125">
-        <v>1.867801535825337E+79</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>1.075187856788275E+59</v>
+        <v>0</v>
       </c>
       <c r="E125">
-        <v>3.244719102067087E+99</v>
+        <v>3639.758</v>
       </c>
       <c r="F125">
-        <v>7.677</v>
+        <v>-1.066</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>0.2865</v>
       </c>
     </row>
     <row r="126">
@@ -3648,20 +3736,20 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_1 auto`</t>
+          <t>`p19comuna_Comuna 3 - Manrique`</t>
         </is>
       </c>
       <c r="C126">
-        <v>1.384183325392031E+165</v>
+        <v>0</v>
       </c>
       <c r="D126">
-        <v>1.137940334025791E+143</v>
+        <v>0</v>
       </c>
       <c r="E126">
-        <v>1.68371172108389E+187</v>
+        <v>0</v>
       </c>
       <c r="F126">
-        <v>14.656</v>
+        <v>-7.727</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -3675,23 +3763,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_2 o más autos`</t>
+          <t>`p19comuna_Comuna 4 - Aranjuez`</t>
         </is>
       </c>
       <c r="C127">
-        <v>382495.387</v>
+        <v>0</v>
       </c>
       <c r="D127">
         <v>0</v>
       </c>
       <c r="E127">
-        <v>4.803163663885943E+74</v>
+        <v>0</v>
       </c>
       <c r="F127">
-        <v>0.158</v>
+        <v>-4.878</v>
       </c>
       <c r="G127">
-        <v>0.8742</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -3702,7 +3790,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_1 motocicleta`</t>
+          <t>`p19comuna_Comuna 5 - Castilla`</t>
         </is>
       </c>
       <c r="C128">
@@ -3712,13 +3800,13 @@
         <v>0</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>1892.137</v>
       </c>
       <c r="F128">
-        <v>-7.514</v>
+        <v>-1.099</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>0.2719</v>
       </c>
     </row>
     <row r="129">
@@ -3729,27 +3817,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_Sin motocicletas`</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>`p19comuna_Comuna 6 - Doce de Octubre`</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>0</v>
       </c>
       <c r="D129">
-        <v>3.905383361960379E+280</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <v>15.464</v>
       </c>
       <c r="F129">
-        <v>14.439</v>
+        <v>-1.688</v>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>0.0914</v>
       </c>
     </row>
     <row r="130">
@@ -3760,23 +3844,23 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 1 - Popular`</t>
+          <t>`p19comuna_Comuna 7 - Robledo`</t>
         </is>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>145426684.557</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>119.003</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>177717439968551</v>
       </c>
       <c r="F130">
-        <v>-20.943</v>
+        <v>2.628</v>
       </c>
       <c r="G130">
-        <v>0</v>
+        <v>0.0086</v>
       </c>
     </row>
     <row r="131">
@@ -3787,7 +3871,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 10 - La Candelaria`</t>
+          <t>`p19comuna_Comuna 8 - Villa Hermosa`</t>
         </is>
       </c>
       <c r="C131">
@@ -3797,13 +3881,13 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F131">
-        <v>-187505096.103</v>
+        <v>-2.834</v>
       </c>
       <c r="G131">
-        <v>0</v>
+        <v>0.0046</v>
       </c>
     </row>
     <row r="132">
@@ -3814,7 +3898,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 11 - Laureles Estadio`</t>
+          <t>`p19comuna_Comuna 9 - Buenos Aires`</t>
         </is>
       </c>
       <c r="C132">
@@ -3824,13 +3908,13 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="F132">
-        <v>-1.975</v>
+        <v>-4.224</v>
       </c>
       <c r="G132">
-        <v>0.0483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -3841,23 +3925,23 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 12 - La América`</t>
+          <t>`p22_Entre 11 y 15 km`</t>
         </is>
       </c>
       <c r="C133">
-        <v>5.49491716100207E+270</v>
+        <v>49.373</v>
       </c>
       <c r="D133">
-        <v>4.748180327684427E+257</v>
+        <v>0</v>
       </c>
       <c r="E133">
-        <v>6.35909180412278E+283</v>
+        <v>128163773.826</v>
       </c>
       <c r="F133">
-        <v>40.621</v>
+        <v>0.517</v>
       </c>
       <c r="G133">
-        <v>0</v>
+        <v>0.6048</v>
       </c>
     </row>
     <row r="134">
@@ -3868,23 +3952,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 13 - San Javier`</t>
+          <t>`p22_Entre 16 y 20 km`</t>
         </is>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>49376658327883.09</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>11469789.433</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>2.125631339531401E+20</v>
       </c>
       <c r="F134">
-        <v>-157123458.585</v>
+        <v>4.046</v>
       </c>
       <c r="G134">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="135">
@@ -3895,23 +3979,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 14 - El Poblado`</t>
+          <t>`p22_Entre 6 y 10 km`</t>
         </is>
       </c>
       <c r="C135">
-        <v>4.693294633677335E+100</v>
+        <v>687222403.149</v>
       </c>
       <c r="D135">
-        <v>3.737466061822353E+31</v>
+        <v>716.622</v>
       </c>
       <c r="E135">
-        <v>5.893569106488068E+169</v>
+        <v>659028594260317.1</v>
       </c>
       <c r="F135">
-        <v>2.856</v>
+        <v>2.896</v>
       </c>
       <c r="G135">
-        <v>0.0043</v>
+        <v>0.0038</v>
       </c>
     </row>
     <row r="136">
@@ -3922,23 +4006,23 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 15 - Guayabal`</t>
+          <t>`p22_Menos de 5 km`</t>
         </is>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>21695.392</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>47002345916.555</v>
       </c>
       <c r="F136">
-        <v>-9.987</v>
+        <v>1.341</v>
       </c>
       <c r="G136">
-        <v>0</v>
+        <v>0.1798</v>
       </c>
     </row>
     <row r="137">
@@ -3949,23 +4033,23 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 2 - Santa Cruz`</t>
+          <t>`p23_agregado_Compras y trámites`</t>
         </is>
       </c>
       <c r="C137">
-        <v>1963698148.876</v>
+        <v>0</v>
       </c>
       <c r="D137">
-        <v>1240262656.568</v>
+        <v>0</v>
       </c>
       <c r="E137">
-        <v>3109107897.007</v>
+        <v>1.173</v>
       </c>
       <c r="F137">
-        <v>91.27200000000001</v>
+        <v>-1.92</v>
       </c>
       <c r="G137">
-        <v>0</v>
+        <v>0.0548</v>
       </c>
     </row>
     <row r="138">
@@ -3976,7 +4060,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 3 - Manrique`</t>
+          <t>`p23_agregado_Cuidado y familia`</t>
         </is>
       </c>
       <c r="C138">
@@ -3986,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>64.214</v>
       </c>
       <c r="F138">
-        <v>-113.508</v>
+        <v>-1.511</v>
       </c>
       <c r="G138">
-        <v>0</v>
+        <v>0.1307</v>
       </c>
     </row>
     <row r="139">
@@ -4003,20 +4087,20 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 4 - Aranjuez`</t>
+          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
         </is>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>1.444154130221228E+26</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>7.159694199679645E+19</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>2.912947248401106E+32</v>
       </c>
       <c r="F139">
-        <v>-24.653</v>
+        <v>8.132</v>
       </c>
       <c r="G139">
         <v>0</v>
@@ -4030,20 +4114,20 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 5 - Castilla`</t>
+          <t>`p23_agregado_Visitas sociales`</t>
         </is>
       </c>
       <c r="C140">
-        <v>1.330138620106585E+93</v>
+        <v>3800342973642744</v>
       </c>
       <c r="D140">
-        <v>1.782372772191547E+92</v>
+        <v>120592380.584</v>
       </c>
       <c r="E140">
-        <v>9.926479894122345E+93</v>
+        <v>1.197638411930686E+23</v>
       </c>
       <c r="F140">
-        <v>209.1</v>
+        <v>4.072</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -4057,23 +4141,23 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 6 - Doce de Octubre`</t>
+          <t>`p7_agregado_Desocupado o inactivo`</t>
         </is>
       </c>
       <c r="C141">
-        <v>1.970984807540822E+129</v>
+        <v>52452136922.217</v>
       </c>
       <c r="D141">
-        <v>1.179615439281678E+61</v>
+        <v>1023609.123</v>
       </c>
       <c r="E141">
-        <v>3.293260652744891E+197</v>
+        <v>2687770757695367</v>
       </c>
       <c r="F141">
-        <v>3.715</v>
+        <v>4.461</v>
       </c>
       <c r="G141">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -4084,23 +4168,23 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 7 - Robledo`</t>
+          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
         </is>
       </c>
       <c r="C142">
-        <v>7.317527051859875E+144</v>
+        <v>33358459292.612</v>
       </c>
       <c r="D142">
-        <v>7.263215467482465E+144</v>
+        <v>10219.746</v>
       </c>
       <c r="E142">
-        <v>7.37224475776993E+144</v>
+        <v>1.088859597216713E+17</v>
       </c>
       <c r="F142">
-        <v>87758.35799999999</v>
+        <v>3.166</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="143">
@@ -4111,23 +4195,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 8 - Villa Hermosa`</t>
+          <t>educacion_Secundaria</t>
         </is>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>1769.029</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="E143">
-        <v>929.468</v>
+        <v>41359676.85</v>
       </c>
       <c r="F143">
-        <v>-1.555</v>
+        <v>1.457</v>
       </c>
       <c r="G143">
-        <v>0.12</v>
+        <v>0.1451</v>
       </c>
     </row>
     <row r="144">
@@ -4138,20 +4222,20 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 9 - Buenos Aires`</t>
+          <t>p1edad</t>
         </is>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>5.425</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>2.863</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>10.279</v>
       </c>
       <c r="F144">
-        <v>-5.959</v>
+        <v>5.185</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -4165,7 +4249,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>`p22_Entre 11 y 15 km`</t>
+          <t>p23_agregado_Estudio</t>
         </is>
       </c>
       <c r="C145">
@@ -4175,13 +4259,13 @@
         <v>0</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="F145">
-        <v>-7.132</v>
+        <v>-2.165</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>0.0304</v>
       </c>
     </row>
     <row r="146">
@@ -4192,23 +4276,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>`p22_Entre 16 y 20 km`</t>
+          <t>p24</t>
         </is>
       </c>
       <c r="C146">
-        <v>1.52435247248866E+94</v>
+        <v>0</v>
       </c>
       <c r="D146">
-        <v>1.936740256996905E+26</v>
+        <v>0</v>
       </c>
       <c r="E146">
-        <v>1.199773925278582E+162</v>
+        <v>0</v>
       </c>
       <c r="F146">
-        <v>2.719</v>
+        <v>-10.889</v>
       </c>
       <c r="G146">
-        <v>0.0066</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -4219,23 +4303,23 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>`p22_Entre 6 y 10 km`</t>
+          <t>p28_importancia_comodidad</t>
         </is>
       </c>
       <c r="C147">
-        <v>3.284144205580605E+52</v>
+        <v>1001.462</v>
       </c>
       <c r="D147">
-        <v>42976330175159.98</v>
+        <v>1.032</v>
       </c>
       <c r="E147">
-        <v>2.509661276123226E+91</v>
+        <v>971693.46</v>
       </c>
       <c r="F147">
-        <v>2.647</v>
+        <v>1.969</v>
       </c>
       <c r="G147">
-        <v>0.0081</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="148">
@@ -4246,23 +4330,23 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>`p22_Menos de 5 km`</t>
+          <t>p28_importancia_costo_compra</t>
         </is>
       </c>
       <c r="C148">
-        <v>6.837028283255667E+49</v>
+        <v>224.573</v>
       </c>
       <c r="D148">
-        <v>7.635289473467174E+27</v>
+        <v>2.151</v>
       </c>
       <c r="E148">
-        <v>6.122224430190523E+71</v>
+        <v>23443.803</v>
       </c>
       <c r="F148">
-        <v>4.45</v>
+        <v>2.283</v>
       </c>
       <c r="G148">
-        <v>0</v>
+        <v>0.0224</v>
       </c>
     </row>
     <row r="149">
@@ -4273,23 +4357,23 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>`p23_agregado_Compras y trámites`</t>
+          <t>p28_importancia_costo_uso</t>
         </is>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>2.619</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="E149">
-        <v>315044547034163.6</v>
+        <v>194.87</v>
       </c>
       <c r="F149">
-        <v>-0.895</v>
+        <v>0.438</v>
       </c>
       <c r="G149">
-        <v>0.3708</v>
+        <v>0.6615</v>
       </c>
     </row>
     <row r="150">
@@ -4300,23 +4384,23 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>`p23_agregado_Cuidado y familia`</t>
+          <t>p28_importancia_discriminacion</t>
         </is>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D150">
         <v>0</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="F150">
-        <v>-438.609</v>
+        <v>-3.56</v>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="151">
@@ -4327,26 +4411,20 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>p28_importancia_emisiones</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>1001077.873</v>
+      </c>
+      <c r="D151">
+        <v>5136.033</v>
+      </c>
+      <c r="E151">
+        <v>195122772.405</v>
       </c>
       <c r="F151">
-        <v>23.993</v>
+        <v>5.136</v>
       </c>
       <c r="G151">
         <v>0</v>
@@ -4360,23 +4438,23 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>`p23_agregado_Visitas sociales`</t>
+          <t>p28_importancia_riesgo_acoso</t>
         </is>
       </c>
       <c r="C152">
-        <v>3.114131768136859E+202</v>
+        <v>0.001</v>
       </c>
       <c r="D152">
-        <v>3.381230962245638E+185</v>
+        <v>0</v>
       </c>
       <c r="E152">
-        <v>2.868131984358269E+219</v>
+        <v>0.096</v>
       </c>
       <c r="F152">
-        <v>23.395</v>
+        <v>-3.016</v>
       </c>
       <c r="G152">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="153">
@@ -4387,20 +4465,20 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>`p3_agregado_Población afrodescendiente`</t>
+          <t>p28_importancia_riesgo_robo</t>
         </is>
       </c>
       <c r="C153">
-        <v>1.387749334576066E+278</v>
+        <v>1200727.072</v>
       </c>
       <c r="D153">
-        <v>1.403225872758081E+255</v>
+        <v>9876.152</v>
       </c>
       <c r="E153">
-        <v>1.372443491104538E+301</v>
+        <v>145982518.902</v>
       </c>
       <c r="F153">
-        <v>23.708</v>
+        <v>5.715</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -4414,7 +4492,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>`p3_agregado_Pueblos indígenas`</t>
+          <t>p28_importancia_siniestralidad</t>
         </is>
       </c>
       <c r="C154">
@@ -4426,10 +4504,8 @@
       <c r="E154">
         <v>0</v>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
+      <c r="F154">
+        <v>-7.846</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -4443,20 +4519,20 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>`p3_agregado_Sin respuesta`</t>
+          <t>p28_importancia_tiempo</t>
         </is>
       </c>
       <c r="C155">
-        <v>7.029834069612236E+195</v>
+        <v>0</v>
       </c>
       <c r="D155">
-        <v>1.329977193414943E+180</v>
+        <v>0</v>
       </c>
       <c r="E155">
-        <v>3.715745449693791E+211</v>
+        <v>0</v>
       </c>
       <c r="F155">
-        <v>24.414</v>
+        <v>-5.636</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -4470,24 +4546,20 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>`p5_agregado_Primaria o menos`</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>p32_contaminacion_likert</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>524047705.39</v>
       </c>
       <c r="D156">
-        <v>4.278572910172476E+291</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>20319968.441</v>
+      </c>
+      <c r="E156">
+        <v>13515079923.556</v>
       </c>
       <c r="F156">
-        <v>31.257</v>
+        <v>12.108</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -4501,23 +4573,23 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>`p5_agregado_Técnico / Tecnológico`</t>
+          <t>p38p38_dummy_1</t>
         </is>
       </c>
       <c r="C157">
-        <v>1.094166254154498E+158</v>
+        <v>0</v>
       </c>
       <c r="D157">
-        <v>2.877202896070747E+113</v>
+        <v>0</v>
       </c>
       <c r="E157">
-        <v>4.160984939106805E+202</v>
+        <v>0.079</v>
       </c>
       <c r="F157">
-        <v>6.948</v>
+        <v>-2.585</v>
       </c>
       <c r="G157">
-        <v>0</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="158">
@@ -4528,23 +4600,23 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>`p7_agregado_Desocupado o inactivo`</t>
+          <t>p3_minoria_Sí</t>
         </is>
       </c>
       <c r="C158">
-        <v>5.328498072148561E+232</v>
+        <v>2380824489.422</v>
       </c>
       <c r="D158">
-        <v>1.455676418408719E+204</v>
+        <v>5.848</v>
       </c>
       <c r="E158">
-        <v>1.950494721617487E+261</v>
+        <v>9.691999566611274E+17</v>
       </c>
       <c r="F158">
-        <v>15.969</v>
+        <v>2.135</v>
       </c>
       <c r="G158">
-        <v>0</v>
+        <v>0.0328</v>
       </c>
     </row>
     <row r="159">
@@ -4555,20 +4627,20 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
+          <t>p40_Mujer</t>
         </is>
       </c>
       <c r="C159">
-        <v>2.852122396130774E+49</v>
+        <v>2.202311868963328E+20</v>
       </c>
       <c r="D159">
-        <v>1.660123650189223E+28</v>
+        <v>8611327169590500</v>
       </c>
       <c r="E159">
-        <v>4.899997757145111E+70</v>
+        <v>5.632322954009181E+24</v>
       </c>
       <c r="F159">
-        <v>4.565</v>
+        <v>9.045999999999999</v>
       </c>
       <c r="G159">
         <v>0</v>
@@ -4582,20 +4654,20 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>p1edad</t>
+          <t>p7_agregado_Estudiante</t>
         </is>
       </c>
       <c r="C160">
-        <v>2139051942943.103</v>
+        <v>1.429978048073484E+51</v>
       </c>
       <c r="D160">
-        <v>2980132488.883</v>
+        <v>1.048321651598802E+44</v>
       </c>
       <c r="E160">
-        <v>1535348925484856</v>
+        <v>1.950581879953978E+58</v>
       </c>
       <c r="F160">
-        <v>8.462</v>
+        <v>14.053</v>
       </c>
       <c r="G160">
         <v>0</v>
@@ -4609,7 +4681,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>p23_agregado_Estudio</t>
+          <t>p9_estrato3_Bajo</t>
         </is>
       </c>
       <c r="C161">
@@ -4619,13 +4691,13 @@
         <v>0</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>0.236</v>
       </c>
       <c r="F161">
-        <v>-13.489</v>
+        <v>-2.127</v>
       </c>
       <c r="G161">
-        <v>0</v>
+        <v>0.0334</v>
       </c>
     </row>
     <row r="162">
@@ -4636,23 +4708,23 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>p24</t>
+          <t>p9_estrato3_Medio</t>
         </is>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D162">
         <v>0</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>1067.843</v>
       </c>
       <c r="F162">
-        <v>-16.717</v>
+        <v>-1.002</v>
       </c>
       <c r="G162">
-        <v>0</v>
+        <v>0.3162</v>
       </c>
     </row>
     <row r="163">
@@ -4663,142 +4735,142 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>p28_importancia_comodidad</t>
+          <t>tiempo_total</t>
         </is>
       </c>
       <c r="C163">
-        <v>2.306192261520744E+18</v>
+        <v>0.668</v>
       </c>
       <c r="D163">
-        <v>190.962</v>
+        <v>0.442</v>
       </c>
       <c r="E163">
-        <v>2.785123494167546E+34</v>
+        <v>1.011</v>
       </c>
       <c r="F163">
-        <v>2.238</v>
+        <v>-1.91</v>
       </c>
       <c r="G163">
-        <v>0.0252</v>
+        <v>0.0561</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>p28_importancia_costo_compra</t>
+          <t>(Intercept)</t>
         </is>
       </c>
       <c r="C164">
-        <v>1.226971011068175E+27</v>
+        <v>0</v>
       </c>
       <c r="D164">
         <v>0</v>
       </c>
       <c r="E164">
-        <v>7.253530212180851E+69</v>
+        <v>0</v>
       </c>
       <c r="F164">
-        <v>1.241</v>
+        <v>-7.343</v>
       </c>
       <c r="G164">
-        <v>0.2145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>p28_importancia_costo_uso</t>
+          <t>`edad_r2_18 - 34 años`</t>
         </is>
       </c>
       <c r="C165">
-        <v>1.546010068638546E+17</v>
+        <v>1.305917184056804E+21</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>6935332910919603</v>
       </c>
       <c r="E165">
-        <v>1.027103634447468E+38</v>
+        <v>2.459030753851323E+26</v>
       </c>
       <c r="F165">
-        <v>1.618</v>
+        <v>7.846</v>
       </c>
       <c r="G165">
-        <v>0.1057</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>p28_importancia_discriminacion</t>
+          <t>`edad_r2_55 - 80 años`</t>
         </is>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>2.989</v>
       </c>
       <c r="D166">
         <v>0</v>
       </c>
       <c r="E166">
-        <v>3.087833693488837E+19</v>
+        <v>433502.336</v>
       </c>
       <c r="F166">
-        <v>-0.8120000000000001</v>
+        <v>0.181</v>
       </c>
       <c r="G166">
-        <v>0.4167</v>
+        <v>0.8567</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>p28_importancia_emisiones</t>
+          <t>`educacion_Primaria o menos`</t>
         </is>
       </c>
       <c r="C167">
-        <v>2.041104058624001E+115</v>
+        <v>3839.69</v>
       </c>
       <c r="D167">
-        <v>9.291172705426195E+71</v>
+        <v>0.755</v>
       </c>
       <c r="E167">
-        <v>4.483939659950889E+158</v>
+        <v>19531680.68</v>
       </c>
       <c r="F167">
-        <v>5.215</v>
+        <v>1.895</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>p28_importancia_riesgo_acoso</t>
+          <t>`p15_autos_agregado_1 auto`</t>
         </is>
       </c>
       <c r="C168">
@@ -4808,37 +4880,37 @@
         <v>0</v>
       </c>
       <c r="E168">
-        <v>0</v>
+        <v>0.322</v>
       </c>
       <c r="F168">
-        <v>-4.339</v>
+        <v>-2.19</v>
       </c>
       <c r="G168">
-        <v>0</v>
+        <v>0.0285</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>p28_importancia_riesgo_robo</t>
+          <t>`p15_autos_agregado_2 o más autos`</t>
         </is>
       </c>
       <c r="C169">
-        <v>2.110112703367868E+95</v>
+        <v>0</v>
       </c>
       <c r="D169">
-        <v>8.048268454811998E+64</v>
+        <v>0</v>
       </c>
       <c r="E169">
-        <v>5.532339839201427E+125</v>
+        <v>0</v>
       </c>
       <c r="F169">
-        <v>6.142</v>
+        <v>-4.955</v>
       </c>
       <c r="G169">
         <v>0</v>
@@ -4847,12 +4919,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>p28_importancia_siniestralidad</t>
+          <t>`p16_motos_agregado_1 motocicleta`</t>
         </is>
       </c>
       <c r="C170">
@@ -4865,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="F170">
-        <v>-5.204</v>
+        <v>-4.156</v>
       </c>
       <c r="G170">
         <v>0</v>
@@ -4874,25 +4946,25 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>p28_importancia_tiempo</t>
+          <t>`p16_motos_agregado_Sin motocicletas`</t>
         </is>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>468779331885.269</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>38795084.614</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>5664482090685446</v>
       </c>
       <c r="F171">
-        <v>-8.44</v>
+        <v>5.604</v>
       </c>
       <c r="G171">
         <v>0</v>
@@ -4901,25 +4973,25 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>p32_contaminacion_likert</t>
+          <t>`p19comuna_Comuna 1 - Popular`</t>
         </is>
       </c>
       <c r="C172">
-        <v>4.565649121824321E+137</v>
+        <v>0</v>
       </c>
       <c r="D172">
-        <v>9.476882560363919E+106</v>
+        <v>0</v>
       </c>
       <c r="E172">
-        <v>2.199579004049E+168</v>
+        <v>0</v>
       </c>
       <c r="F172">
-        <v>8.794</v>
+        <v>-5.032</v>
       </c>
       <c r="G172">
         <v>0</v>
@@ -4928,110 +5000,106 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>p36_influencia_amigos</t>
+          <t>`p19comuna_Comuna 10 - La Candelaria`</t>
         </is>
       </c>
       <c r="C173">
-        <v>4.514933178200618E+70</v>
+        <v>1221544311.506</v>
       </c>
       <c r="D173">
-        <v>2.233778563633343E+44</v>
+        <v>14529.504</v>
       </c>
       <c r="E173">
-        <v>9.125623253569151E+96</v>
+        <v>102699341051771.1</v>
       </c>
       <c r="F173">
-        <v>5.264</v>
+        <v>3.617</v>
       </c>
       <c r="G173">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>p37_influencia_familia</t>
+          <t>`p19comuna_Comuna 11 - Laureles Estadio`</t>
         </is>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>571538.571</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E174">
-        <v>4796583648.55</v>
+        <v>326540346331.628</v>
       </c>
       <c r="F174">
-        <v>-1.134</v>
+        <v>1.96</v>
       </c>
       <c r="G174">
-        <v>0.2568</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>p38p38_dummy_1</t>
+          <t>`p19comuna_Comuna 12 - La América`</t>
         </is>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>5.011957584879756E+24</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>8.95722894827577E+17</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>2.804407365010954E+31</v>
       </c>
       <c r="F175">
-        <v>-2.543</v>
+        <v>7.174</v>
       </c>
       <c r="G175">
-        <v>0.011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>p40_Mujer</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>`p19comuna_Comuna 13 - San Javier`</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>1.331541627663602E+26</v>
       </c>
       <c r="D176">
-        <v>6.778848243691476E+280</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>3.965553190787288E+21</v>
+      </c>
+      <c r="E176">
+        <v>4.47101077932846E+30</v>
       </c>
       <c r="F176">
-        <v>15.137</v>
+        <v>11.313</v>
       </c>
       <c r="G176">
         <v>0</v>
@@ -5040,25 +5108,25 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>p5_agregado_Secundaria</t>
+          <t>`p19comuna_Comuna 14 - El Poblado`</t>
         </is>
       </c>
       <c r="C177">
-        <v>3.314114523237052E+212</v>
+        <v>2.106051854817797E+17</v>
       </c>
       <c r="D177">
-        <v>2.918573737471947E+170</v>
+        <v>58488033913.37</v>
       </c>
       <c r="E177">
-        <v>3.763261120359591E+254</v>
+        <v>7.583524557777276E+23</v>
       </c>
       <c r="F177">
-        <v>9.904999999999999</v>
+        <v>5.179</v>
       </c>
       <c r="G177">
         <v>0</v>
@@ -5067,115 +5135,109 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>p7_agregado_Estudiante</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>`p19comuna_Comuna 15 - Guayabal`</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>93.46599999999999</v>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+      <c r="E178">
+        <v>85789367.27500001</v>
       </c>
       <c r="F178">
-        <v>36.779</v>
+        <v>0.648</v>
       </c>
       <c r="G178">
-        <v>0</v>
+        <v>0.5171</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>p9_estrato3_Bajo</t>
+          <t>`p19comuna_Comuna 2 - Santa Cruz`</t>
         </is>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>298967.934</v>
       </c>
       <c r="D179">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>523594455654.242</v>
       </c>
       <c r="F179">
-        <v>-15.928</v>
+        <v>1.719</v>
       </c>
       <c r="G179">
-        <v>0</v>
+        <v>0.0856</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>p9_estrato3_Medio</t>
+          <t>`p19comuna_Comuna 3 - Manrique`</t>
         </is>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>179.076</v>
       </c>
       <c r="D180">
         <v>0</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>1446109720.11</v>
       </c>
       <c r="F180">
-        <v>-19.942</v>
+        <v>0.639</v>
       </c>
       <c r="G180">
-        <v>0</v>
+        <v>0.5226</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>tiempo_total</t>
+          <t>`p19comuna_Comuna 4 - Aranjuez`</t>
         </is>
       </c>
       <c r="C181">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D181">
         <v>0</v>
       </c>
       <c r="E181">
-        <v>8.616</v>
+        <v>24.676</v>
       </c>
       <c r="F181">
-        <v>-1.512</v>
+        <v>-1.418</v>
       </c>
       <c r="G181">
-        <v>0.1304</v>
+        <v>0.1561</v>
       </c>
     </row>
     <row r="182">
@@ -5186,20 +5248,20 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>(Intercept)</t>
+          <t>`p19comuna_Comuna 5 - Castilla`</t>
         </is>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>7.129640556784117E+20</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>61253113117392.21</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>8.298643429195398E+27</v>
       </c>
       <c r="F182">
-        <v>-22.553</v>
+        <v>5.784</v>
       </c>
       <c r="G182">
         <v>0</v>
@@ -5213,27 +5275,23 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>`edad_r2_18 - 34 años`</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>`p19comuna_Comuna 6 - Doce de Octubre`</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>62.444</v>
       </c>
       <c r="D183">
-        <v>1.05788014048793E+294</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.001</v>
+      </c>
+      <c r="E183">
+        <v>3369086.931</v>
       </c>
       <c r="F183">
-        <v>11.593</v>
+        <v>0.744</v>
       </c>
       <c r="G183">
-        <v>0</v>
+        <v>0.4571</v>
       </c>
     </row>
     <row r="184">
@@ -5244,23 +5302,23 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>`edad_r2_55 - 80 años`</t>
+          <t>`p19comuna_Comuna 7 - Robledo`</t>
         </is>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>99433.70699999999</v>
       </c>
       <c r="D184">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="E184">
-        <v>0</v>
+        <v>11907665975.033</v>
       </c>
       <c r="F184">
-        <v>-3.857</v>
+        <v>1.929</v>
       </c>
       <c r="G184">
-        <v>0.0001</v>
+        <v>0.0538</v>
       </c>
     </row>
     <row r="185">
@@ -5271,23 +5329,23 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>`p12_dificultad_binaria_Con alguna dificultad`</t>
+          <t>`p19comuna_Comuna 8 - Villa Hermosa`</t>
         </is>
       </c>
       <c r="C185">
-        <v>1.572632608653239E+66</v>
+        <v>0.121</v>
       </c>
       <c r="D185">
-        <v>1.443556132097861E+46</v>
+        <v>0</v>
       </c>
       <c r="E185">
-        <v>1.713250539281327E+86</v>
+        <v>74310423.771</v>
       </c>
       <c r="F185">
-        <v>6.475</v>
+        <v>-0.205</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>0.8379</v>
       </c>
     </row>
     <row r="186">
@@ -5298,23 +5356,23 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_1 auto`</t>
+          <t>`p19comuna_Comuna 9 - Buenos Aires`</t>
         </is>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>32525.845</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E186">
-        <v>12287956303612.26</v>
+        <v>52045060476.226</v>
       </c>
       <c r="F186">
-        <v>-1.589</v>
+        <v>1.425</v>
       </c>
       <c r="G186">
-        <v>0.112</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="187">
@@ -5325,23 +5383,23 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_2 o más autos`</t>
+          <t>`p22_Entre 11 y 15 km`</t>
         </is>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>1.352</v>
       </c>
       <c r="D187">
         <v>0</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>9955.143</v>
       </c>
       <c r="F187">
-        <v>-926502580.298</v>
+        <v>0.066</v>
       </c>
       <c r="G187">
-        <v>0</v>
+        <v>0.9471000000000001</v>
       </c>
     </row>
     <row r="188">
@@ -5352,23 +5410,23 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_1 motocicleta`</t>
+          <t>`p22_Entre 16 y 20 km`</t>
         </is>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>3277.762</v>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>414778873.031</v>
       </c>
       <c r="F188">
-        <v>-7.456</v>
+        <v>1.35</v>
       </c>
       <c r="G188">
-        <v>0</v>
+        <v>0.1769</v>
       </c>
     </row>
     <row r="189">
@@ -5379,23 +5437,23 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_Sin motocicletas`</t>
+          <t>`p22_Entre 6 y 10 km`</t>
         </is>
       </c>
       <c r="C189">
-        <v>1.861202259864672E+194</v>
+        <v>340627702.732</v>
       </c>
       <c r="D189">
-        <v>6.115772719362012E+168</v>
+        <v>11158.678</v>
       </c>
       <c r="E189">
-        <v>5.664163812298648E+219</v>
+        <v>10397936834423.24</v>
       </c>
       <c r="F189">
-        <v>14.942</v>
+        <v>3.729</v>
       </c>
       <c r="G189">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="190">
@@ -5406,20 +5464,20 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 1 - Popular`</t>
+          <t>`p22_Menos de 5 km`</t>
         </is>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>9074981563946.273</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>57846949.376</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>1.423675600422512E+18</v>
       </c>
       <c r="F190">
-        <v>-11.941</v>
+        <v>4.888</v>
       </c>
       <c r="G190">
         <v>0</v>
@@ -5433,23 +5491,23 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 10 - La Candelaria`</t>
+          <t>`p23_agregado_Compras y trámites`</t>
         </is>
       </c>
       <c r="C191">
-        <v>4605569.838</v>
+        <v>0</v>
       </c>
       <c r="D191">
         <v>0</v>
       </c>
       <c r="E191">
-        <v>2.936831738465398E+32</v>
+        <v>0</v>
       </c>
       <c r="F191">
-        <v>0.506</v>
+        <v>-4.569</v>
       </c>
       <c r="G191">
-        <v>0.6128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -5460,23 +5518,23 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 11 - Laureles Estadio`</t>
+          <t>`p23_agregado_Cuidado y familia`</t>
         </is>
       </c>
       <c r="C192">
-        <v>1938132633182.383</v>
+        <v>0</v>
       </c>
       <c r="D192">
         <v>0</v>
       </c>
       <c r="E192">
-        <v>2.679360943093609E+38</v>
+        <v>0</v>
       </c>
       <c r="F192">
-        <v>0.921</v>
+        <v>-5.462</v>
       </c>
       <c r="G192">
-        <v>0.3569</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -5487,23 +5545,23 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 12 - La América`</t>
+          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
         </is>
       </c>
       <c r="C193">
-        <v>2.430679447616861E+152</v>
+        <v>675202923382.474</v>
       </c>
       <c r="D193">
-        <v>2.100360023259333E+139</v>
+        <v>62072.964</v>
       </c>
       <c r="E193">
-        <v>2.812947547867854E+165</v>
+        <v>7.34456605735855E+18</v>
       </c>
       <c r="F193">
-        <v>22.864</v>
+        <v>3.295</v>
       </c>
       <c r="G193">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="194">
@@ -5514,26 +5572,20 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 13 - San Javier`</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>`p23_agregado_Visitas sociales`</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="E194">
+        <v>0</v>
       </c>
       <c r="F194">
-        <v>102777311.563</v>
+        <v>-4.332</v>
       </c>
       <c r="G194">
         <v>0</v>
@@ -5547,20 +5599,20 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 14 - El Poblado`</t>
+          <t>`p7_agregado_Desocupado o inactivo`</t>
         </is>
       </c>
       <c r="C195">
-        <v>1.172933073772021E+189</v>
+        <v>21948611506821.29</v>
       </c>
       <c r="D195">
-        <v>3.189337570256605E+188</v>
+        <v>128828024.905</v>
       </c>
       <c r="E195">
-        <v>4.313660643447002E+189</v>
+        <v>3.739415763249702E+18</v>
       </c>
       <c r="F195">
-        <v>655.222</v>
+        <v>4.999</v>
       </c>
       <c r="G195">
         <v>0</v>
@@ -5574,23 +5626,23 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 15 - Guayabal`</t>
+          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
         </is>
       </c>
       <c r="C196">
-        <v>0</v>
+        <v>3.636655651126657E+18</v>
       </c>
       <c r="D196">
-        <v>0</v>
+        <v>36659357025423.54</v>
       </c>
       <c r="E196">
-        <v>4.689082604166168E+41</v>
+        <v>3.607609461262408E+23</v>
       </c>
       <c r="F196">
-        <v>-0.517</v>
+        <v>7.281</v>
       </c>
       <c r="G196">
-        <v>0.6051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -5601,23 +5653,23 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 2 - Santa Cruz`</t>
+          <t>educacion_Secundaria</t>
         </is>
       </c>
       <c r="C197">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D197">
         <v>0</v>
       </c>
       <c r="E197">
-        <v>1.441259393926105E+35</v>
+        <v>0.3</v>
       </c>
       <c r="F197">
-        <v>-0.164</v>
+        <v>-2.269</v>
       </c>
       <c r="G197">
-        <v>0.8695000000000001</v>
+        <v>0.0233</v>
       </c>
     </row>
     <row r="198">
@@ -5628,23 +5680,23 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 3 - Manrique`</t>
+          <t>p1edad</t>
         </is>
       </c>
       <c r="C198">
-        <v>28289429.883</v>
+        <v>4.477</v>
       </c>
       <c r="D198">
-        <v>0</v>
+        <v>2.961</v>
       </c>
       <c r="E198">
-        <v>1.024612291584776E+46</v>
+        <v>6.771</v>
       </c>
       <c r="F198">
-        <v>0.379</v>
+        <v>7.103</v>
       </c>
       <c r="G198">
-        <v>0.7049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -5655,23 +5707,23 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 4 - Aranjuez`</t>
+          <t>p23_agregado_Estudio</t>
         </is>
       </c>
       <c r="C199">
-        <v>0</v>
+        <v>336.806</v>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>0.097</v>
       </c>
       <c r="E199">
-        <v>140.137</v>
+        <v>1163903.523</v>
       </c>
       <c r="F199">
-        <v>-1.822</v>
+        <v>1.4</v>
       </c>
       <c r="G199">
-        <v>0.06850000000000001</v>
+        <v>0.1615</v>
       </c>
     </row>
     <row r="200">
@@ -5682,20 +5734,20 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 5 - Castilla`</t>
+          <t>p24</t>
         </is>
       </c>
       <c r="C200">
-        <v>5.280349681095342E+196</v>
+        <v>0</v>
       </c>
       <c r="D200">
-        <v>7.076524440040297E+195</v>
+        <v>0</v>
       </c>
       <c r="E200">
-        <v>3.940082874141096E+197</v>
+        <v>0</v>
       </c>
       <c r="F200">
-        <v>441.748</v>
+        <v>-5.034</v>
       </c>
       <c r="G200">
         <v>0</v>
@@ -5709,23 +5761,23 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 6 - Doce de Octubre`</t>
+          <t>p28_importancia_comodidad</t>
         </is>
       </c>
       <c r="C201">
-        <v>112.182</v>
+        <v>0</v>
       </c>
       <c r="D201">
         <v>0</v>
       </c>
       <c r="E201">
-        <v>2.263211277141419E+32</v>
+        <v>0.297</v>
       </c>
       <c r="F201">
-        <v>0.133</v>
+        <v>-2.324</v>
       </c>
       <c r="G201">
-        <v>0.8945</v>
+        <v>0.0201</v>
       </c>
     </row>
     <row r="202">
@@ -5736,23 +5788,23 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 7 - Robledo`</t>
+          <t>p28_importancia_costo_compra</t>
         </is>
       </c>
       <c r="C202">
-        <v>1.150275039982081E+68</v>
+        <v>17988.144</v>
       </c>
       <c r="D202">
-        <v>7244300071066225</v>
+        <v>284.491</v>
       </c>
       <c r="E202">
-        <v>1.82644652295724E+120</v>
+        <v>1137378.165</v>
       </c>
       <c r="F202">
-        <v>2.556</v>
+        <v>4.631</v>
       </c>
       <c r="G202">
-        <v>0.0106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -5763,7 +5815,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 8 - Villa Hermosa`</t>
+          <t>p28_importancia_costo_uso</t>
         </is>
       </c>
       <c r="C203">
@@ -5773,10 +5825,10 @@
         <v>0</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="F203">
-        <v>-21.286</v>
+        <v>-5.696</v>
       </c>
       <c r="G203">
         <v>0</v>
@@ -5790,23 +5842,23 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 9 - Buenos Aires`</t>
+          <t>p28_importancia_discriminacion</t>
         </is>
       </c>
       <c r="C204">
-        <v>2.884131574023628E+166</v>
+        <v>0.003</v>
       </c>
       <c r="D204">
-        <v>6.349369643085942E+122</v>
+        <v>0</v>
       </c>
       <c r="E204">
-        <v>1.310085158664217E+210</v>
+        <v>0.147</v>
       </c>
       <c r="F204">
-        <v>7.473</v>
+        <v>-2.928</v>
       </c>
       <c r="G204">
-        <v>0</v>
+        <v>0.0034</v>
       </c>
     </row>
     <row r="205">
@@ -5817,23 +5869,23 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>`p22_Entre 11 y 15 km`</t>
+          <t>p28_importancia_emisiones</t>
         </is>
       </c>
       <c r="C205">
-        <v>0</v>
+        <v>2768478.774</v>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>49181.739</v>
       </c>
       <c r="E205">
-        <v>0</v>
+        <v>155839848.378</v>
       </c>
       <c r="F205">
-        <v>-3.287</v>
+        <v>7.214</v>
       </c>
       <c r="G205">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -5844,23 +5896,23 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>`p22_Entre 16 y 20 km`</t>
+          <t>p28_importancia_riesgo_acoso</t>
         </is>
       </c>
       <c r="C206">
-        <v>4082751836.567</v>
+        <v>216.493</v>
       </c>
       <c r="D206">
-        <v>1.117</v>
+        <v>5.457</v>
       </c>
       <c r="E206">
-        <v>1.491844014472019E+19</v>
+        <v>8589.178</v>
       </c>
       <c r="F206">
-        <v>1.97</v>
+        <v>2.864</v>
       </c>
       <c r="G206">
-        <v>0.0489</v>
+        <v>0.0042</v>
       </c>
     </row>
     <row r="207">
@@ -5871,23 +5923,23 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>`p22_Entre 6 y 10 km`</t>
+          <t>p28_importancia_riesgo_robo</t>
         </is>
       </c>
       <c r="C207">
-        <v>7.665826847094243E+112</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D207">
-        <v>5.745326933527983E+66</v>
+        <v>0.004</v>
       </c>
       <c r="E207">
-        <v>1.022829543549502E+159</v>
+        <v>1.825</v>
       </c>
       <c r="F207">
-        <v>4.797</v>
+        <v>-1.572</v>
       </c>
       <c r="G207">
-        <v>0</v>
+        <v>0.1159</v>
       </c>
     </row>
     <row r="208">
@@ -5898,20 +5950,20 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>`p22_Menos de 5 km`</t>
+          <t>p28_importancia_siniestralidad</t>
         </is>
       </c>
       <c r="C208">
-        <v>1.749900054879473E+181</v>
+        <v>0</v>
       </c>
       <c r="D208">
-        <v>4.853062421608473E+161</v>
+        <v>0</v>
       </c>
       <c r="E208">
-        <v>6.309727623598708E+200</v>
+        <v>0</v>
       </c>
       <c r="F208">
-        <v>18.164</v>
+        <v>-8.202999999999999</v>
       </c>
       <c r="G208">
         <v>0</v>
@@ -5925,23 +5977,23 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>`p23_agregado_Compras y trámites`</t>
+          <t>p28_importancia_tiempo</t>
         </is>
       </c>
       <c r="C209">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="D209">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="E209">
-        <v>0</v>
+        <v>3451.539</v>
       </c>
       <c r="F209">
-        <v>-3.798</v>
+        <v>0.641</v>
       </c>
       <c r="G209">
-        <v>0.0001</v>
+        <v>0.5214</v>
       </c>
     </row>
     <row r="210">
@@ -5952,23 +6004,23 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>`p23_agregado_Cuidado y familia`</t>
+          <t>p32_contaminacion_likert</t>
         </is>
       </c>
       <c r="C210">
-        <v>0</v>
+        <v>4.573</v>
       </c>
       <c r="D210">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="E210">
-        <v>0</v>
+        <v>194.512</v>
       </c>
       <c r="F210">
-        <v>-450.761</v>
+        <v>0.794</v>
       </c>
       <c r="G210">
-        <v>0</v>
+        <v>0.4269</v>
       </c>
     </row>
     <row r="211">
@@ -5979,23 +6031,23 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
+          <t>p38p38_dummy_1</t>
         </is>
       </c>
       <c r="C211">
-        <v>2.05185916212994E+215</v>
+        <v>0.001</v>
       </c>
       <c r="D211">
-        <v>2.890062922045E+186</v>
+        <v>0</v>
       </c>
       <c r="E211">
-        <v>1.456759293751815E+244</v>
+        <v>0.299</v>
       </c>
       <c r="F211">
-        <v>14.627</v>
+        <v>-2.365</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="212">
@@ -6006,23 +6058,23 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>`p23_agregado_Visitas sociales`</t>
+          <t>p3_minoria_Sí</t>
         </is>
       </c>
       <c r="C212">
-        <v>0</v>
+        <v>192512265.477</v>
       </c>
       <c r="D212">
-        <v>0</v>
+        <v>14.301</v>
       </c>
       <c r="E212">
-        <v>0</v>
+        <v>2591506464329128</v>
       </c>
       <c r="F212">
-        <v>-5.123</v>
+        <v>2.278</v>
       </c>
       <c r="G212">
-        <v>0</v>
+        <v>0.0227</v>
       </c>
     </row>
     <row r="213">
@@ -6033,20 +6085,20 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>`p3_agregado_Población afrodescendiente`</t>
+          <t>p40_Mujer</t>
         </is>
       </c>
       <c r="C213">
-        <v>1.457074701233078E+188</v>
+        <v>111678.895</v>
       </c>
       <c r="D213">
-        <v>3.91845901647149E+165</v>
+        <v>441.629</v>
       </c>
       <c r="E213">
-        <v>5.418116346372437E+210</v>
+        <v>28241289.784</v>
       </c>
       <c r="F213">
-        <v>16.34</v>
+        <v>4.118</v>
       </c>
       <c r="G213">
         <v>0</v>
@@ -6060,20 +6112,20 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>`p3_agregado_Pueblos indígenas`</t>
+          <t>p7_agregado_Estudiante</t>
         </is>
       </c>
       <c r="C214">
-        <v>0</v>
+        <v>1.153872331496017E+25</v>
       </c>
       <c r="D214">
-        <v>0</v>
+        <v>4.083597812320454E+18</v>
       </c>
       <c r="E214">
-        <v>0</v>
+        <v>3.260412554280142E+31</v>
       </c>
       <c r="F214">
-        <v>-2.86795175815342E+146</v>
+        <v>7.614</v>
       </c>
       <c r="G214">
         <v>0</v>
@@ -6087,23 +6139,23 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>`p3_agregado_Sin respuesta`</t>
+          <t>p9_estrato3_Bajo</t>
         </is>
       </c>
       <c r="C215">
-        <v>3.405381785179212E+53</v>
+        <v>76337.43799999999</v>
       </c>
       <c r="D215">
-        <v>50202936214651.02</v>
+        <v>0.075</v>
       </c>
       <c r="E215">
-        <v>2.309949572122048E+93</v>
+        <v>77227994607.401</v>
       </c>
       <c r="F215">
-        <v>2.634</v>
+        <v>1.594</v>
       </c>
       <c r="G215">
-        <v>0.008399999999999999</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="216">
@@ -6114,23 +6166,23 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>`p5_agregado_Primaria o menos`</t>
+          <t>p9_estrato3_Medio</t>
         </is>
       </c>
       <c r="C216">
-        <v>0</v>
+        <v>526675.067</v>
       </c>
       <c r="D216">
-        <v>0</v>
+        <v>3.976</v>
       </c>
       <c r="E216">
-        <v>0</v>
+        <v>69762005945.55701</v>
       </c>
       <c r="F216">
-        <v>-11.002</v>
+        <v>2.189</v>
       </c>
       <c r="G216">
-        <v>0</v>
+        <v>0.0286</v>
       </c>
     </row>
     <row r="217">
@@ -6141,676 +6193,22 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>`p5_agregado_Técnico / Tecnológico`</t>
+          <t>tiempo_total</t>
         </is>
       </c>
       <c r="C217">
-        <v>0</v>
+        <v>3.616</v>
       </c>
       <c r="D217">
-        <v>0</v>
+        <v>2.666</v>
       </c>
       <c r="E217">
-        <v>0</v>
+        <v>4.905</v>
       </c>
       <c r="F217">
-        <v>-9.173999999999999</v>
+        <v>8.263</v>
       </c>
       <c r="G217">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>`p7_agregado_Desocupado o inactivo`</t>
-        </is>
-      </c>
-      <c r="C218">
-        <v>1.888479476393311E+223</v>
-      </c>
-      <c r="D218">
-        <v>9.457665069561827E+188</v>
-      </c>
-      <c r="E218">
-        <v>3.770861736515252E+257</v>
-      </c>
-      <c r="F218">
-        <v>12.759</v>
-      </c>
-      <c r="G218">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
-        </is>
-      </c>
-      <c r="C219">
-        <v>8.996804537763793E+154</v>
-      </c>
-      <c r="D219">
-        <v>1.234056449209131E+120</v>
-      </c>
-      <c r="E219">
-        <v>6.559059104840846E+189</v>
-      </c>
-      <c r="F219">
-        <v>8.712</v>
-      </c>
-      <c r="G219">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>p1edad</t>
-        </is>
-      </c>
-      <c r="C220">
-        <v>33267159536.003</v>
-      </c>
-      <c r="D220">
-        <v>1570116028.792</v>
-      </c>
-      <c r="E220">
-        <v>704854853590.361</v>
-      </c>
-      <c r="F220">
-        <v>15.552</v>
-      </c>
-      <c r="G220">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>p23_agregado_Estudio</t>
-        </is>
-      </c>
-      <c r="C221">
-        <v>2.717721685202878E+99</v>
-      </c>
-      <c r="D221">
-        <v>3.777035064328877E+74</v>
-      </c>
-      <c r="E221">
-        <v>1.955505054209592E+124</v>
-      </c>
-      <c r="F221">
-        <v>7.84</v>
-      </c>
-      <c r="G221">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>p24</t>
-        </is>
-      </c>
-      <c r="C222">
-        <v>0</v>
-      </c>
-      <c r="D222">
-        <v>0</v>
-      </c>
-      <c r="E222">
-        <v>0</v>
-      </c>
-      <c r="F222">
-        <v>-6.207</v>
-      </c>
-      <c r="G222">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>p28_importancia_comodidad</t>
-        </is>
-      </c>
-      <c r="C223">
-        <v>0</v>
-      </c>
-      <c r="D223">
-        <v>0</v>
-      </c>
-      <c r="E223">
-        <v>0</v>
-      </c>
-      <c r="F223">
-        <v>-2.894</v>
-      </c>
-      <c r="G223">
-        <v>0.0038</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>p28_importancia_costo_compra</t>
-        </is>
-      </c>
-      <c r="C224">
-        <v>1.078016121277751E+59</v>
-      </c>
-      <c r="D224">
-        <v>1.69320526323798E+24</v>
-      </c>
-      <c r="E224">
-        <v>6.863425143814893E+93</v>
-      </c>
-      <c r="F224">
-        <v>3.324</v>
-      </c>
-      <c r="G224">
-        <v>0.0009</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>p28_importancia_costo_uso</t>
-        </is>
-      </c>
-      <c r="C225">
-        <v>0</v>
-      </c>
-      <c r="D225">
-        <v>0</v>
-      </c>
-      <c r="E225">
-        <v>0.001</v>
-      </c>
-      <c r="F225">
-        <v>-2.141</v>
-      </c>
-      <c r="G225">
-        <v>0.0323</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>p28_importancia_discriminacion</t>
-        </is>
-      </c>
-      <c r="C226">
-        <v>0</v>
-      </c>
-      <c r="D226">
-        <v>0</v>
-      </c>
-      <c r="E226">
-        <v>0</v>
-      </c>
-      <c r="F226">
-        <v>-3.58</v>
-      </c>
-      <c r="G226">
-        <v>0.0003</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>p28_importancia_emisiones</t>
-        </is>
-      </c>
-      <c r="C227">
-        <v>2.022410686910314E+84</v>
-      </c>
-      <c r="D227">
-        <v>9.536447948557044E+67</v>
-      </c>
-      <c r="E227">
-        <v>4.288960636699041E+100</v>
-      </c>
-      <c r="F227">
-        <v>10.121</v>
-      </c>
-      <c r="G227">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>p28_importancia_riesgo_acoso</t>
-        </is>
-      </c>
-      <c r="C228">
-        <v>7.643191009821507E+36</v>
-      </c>
-      <c r="D228">
-        <v>25.1</v>
-      </c>
-      <c r="E228">
-        <v>2.327387485529454E+72</v>
-      </c>
-      <c r="F228">
-        <v>2.037</v>
-      </c>
-      <c r="G228">
-        <v>0.0416</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>p28_importancia_riesgo_robo</t>
-        </is>
-      </c>
-      <c r="C229">
-        <v>0</v>
-      </c>
-      <c r="D229">
-        <v>0</v>
-      </c>
-      <c r="E229">
-        <v>81313291481.465</v>
-      </c>
-      <c r="F229">
-        <v>-1.311</v>
-      </c>
-      <c r="G229">
-        <v>0.1899</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>p28_importancia_siniestralidad</t>
-        </is>
-      </c>
-      <c r="C230">
-        <v>0</v>
-      </c>
-      <c r="D230">
-        <v>0</v>
-      </c>
-      <c r="E230">
-        <v>0</v>
-      </c>
-      <c r="F230">
-        <v>-10.437</v>
-      </c>
-      <c r="G230">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>p28_importancia_tiempo</t>
-        </is>
-      </c>
-      <c r="C231">
-        <v>0</v>
-      </c>
-      <c r="D231">
-        <v>0</v>
-      </c>
-      <c r="E231">
-        <v>1.888252859260611E+21</v>
-      </c>
-      <c r="F231">
-        <v>-1.087</v>
-      </c>
-      <c r="G231">
-        <v>0.2769</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>p32_contaminacion_likert</t>
-        </is>
-      </c>
-      <c r="C232">
-        <v>1.492880515922753E+17</v>
-      </c>
-      <c r="D232">
-        <v>2.204</v>
-      </c>
-      <c r="E232">
-        <v>1.011216459381986E+34</v>
-      </c>
-      <c r="F232">
-        <v>2</v>
-      </c>
-      <c r="G232">
-        <v>0.0455</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>p36_influencia_amigos</t>
-        </is>
-      </c>
-      <c r="C233">
-        <v>9.405642345402156E+54</v>
-      </c>
-      <c r="D233">
-        <v>2.508434911977617E+30</v>
-      </c>
-      <c r="E233">
-        <v>3.526745203042778E+79</v>
-      </c>
-      <c r="F233">
-        <v>4.385</v>
-      </c>
-      <c r="G233">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>p37_influencia_familia</t>
-        </is>
-      </c>
-      <c r="C234">
-        <v>0</v>
-      </c>
-      <c r="D234">
-        <v>0</v>
-      </c>
-      <c r="E234">
-        <v>0</v>
-      </c>
-      <c r="F234">
-        <v>-7.579</v>
-      </c>
-      <c r="G234">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>p38p38_dummy_1</t>
-        </is>
-      </c>
-      <c r="C235">
-        <v>0</v>
-      </c>
-      <c r="D235">
-        <v>0</v>
-      </c>
-      <c r="E235">
-        <v>0</v>
-      </c>
-      <c r="F235">
-        <v>-4.869</v>
-      </c>
-      <c r="G235">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>p40_Mujer</t>
-        </is>
-      </c>
-      <c r="C236">
-        <v>1.939229421328143E+118</v>
-      </c>
-      <c r="D236">
-        <v>3.789377738018017E+80</v>
-      </c>
-      <c r="E236">
-        <v>9.92408518901476E+155</v>
-      </c>
-      <c r="F236">
-        <v>6.148</v>
-      </c>
-      <c r="G236">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>p5_agregado_Secundaria</t>
-        </is>
-      </c>
-      <c r="C237">
-        <v>0</v>
-      </c>
-      <c r="D237">
-        <v>0</v>
-      </c>
-      <c r="E237">
-        <v>0</v>
-      </c>
-      <c r="F237">
-        <v>-8.086</v>
-      </c>
-      <c r="G237">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>p7_agregado_Estudiante</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="F238">
-        <v>16.783</v>
-      </c>
-      <c r="G238">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>p9_estrato3_Bajo</t>
-        </is>
-      </c>
-      <c r="C239">
-        <v>4.496183531075771E+35</v>
-      </c>
-      <c r="D239">
-        <v>5.109705923181696E+17</v>
-      </c>
-      <c r="E239">
-        <v>3.956326772819278E+53</v>
-      </c>
-      <c r="F239">
-        <v>3.894</v>
-      </c>
-      <c r="G239">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>p9_estrato3_Medio</t>
-        </is>
-      </c>
-      <c r="C240">
-        <v>1.653588846282818E+65</v>
-      </c>
-      <c r="D240">
-        <v>1.154590221554994E+34</v>
-      </c>
-      <c r="E240">
-        <v>2.368248077545962E+96</v>
-      </c>
-      <c r="F240">
-        <v>4.103</v>
-      </c>
-      <c r="G240">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>tiempo_total</t>
-        </is>
-      </c>
-      <c r="C241">
-        <v>4981438219.452</v>
-      </c>
-      <c r="D241">
-        <v>113439415.479</v>
-      </c>
-      <c r="E241">
-        <v>218748718242.605</v>
-      </c>
-      <c r="F241">
-        <v>11.571</v>
-      </c>
-      <c r="G241">
         <v>0</v>
       </c>
     </row>
@@ -6821,7 +6219,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BB5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6887,240 +6285,210 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>p36_influencia_amigos</t>
+          <t>tiempo_total</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>p37_influencia_familia</t>
+          <t>p1edad</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>tiempo_total</t>
+          <t>`edad_r2_18 - 34 años`</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>p1edad</t>
+          <t>`edad_r2_55 - 80 años`</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>`edad_r2_18 - 34 años`</t>
+          <t>p3_minoria_Sí</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>`edad_r2_55 - 80 años`</t>
+          <t>educacion_Secundaria</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>`p3_agregado_Población afrodescendiente`</t>
+          <t>`educacion_Primaria o menos`</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>`p3_agregado_Sin respuesta`</t>
+          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>`p3_agregado_Pueblos indígenas`</t>
+          <t>`p7_agregado_Desocupado o inactivo`</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>p5_agregado_Secundaria</t>
+          <t>p7_agregado_Estudiante</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>`p5_agregado_Primaria o menos`</t>
+          <t>p9_estrato3_Medio</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>`p5_agregado_Técnico / Tecnológico`</t>
+          <t>p9_estrato3_Bajo</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
+          <t>p40_Mujer</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>`p7_agregado_Desocupado o inactivo`</t>
+          <t>`p15_autos_agregado_1 auto`</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>p7_agregado_Estudiante</t>
+          <t>`p15_autos_agregado_2 o más autos`</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>p9_estrato3_Medio</t>
+          <t>`p16_motos_agregado_Sin motocicletas`</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>p9_estrato3_Bajo</t>
+          <t>`p16_motos_agregado_1 motocicleta`</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>`p12_dificultad_binaria_Con alguna dificultad`</t>
+          <t>`p22_Entre 16 y 20 km`</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>p40_Mujer</t>
+          <t>`p22_Entre 11 y 15 km`</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_1 auto`</t>
+          <t>`p22_Entre 6 y 10 km`</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_2 o más autos`</t>
+          <t>`p22_Menos de 5 km`</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_Sin motocicletas`</t>
+          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_1 motocicleta`</t>
+          <t>`p23_agregado_Compras y trámites`</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>`p22_Entre 16 y 20 km`</t>
+          <t>p23_agregado_Estudio</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>`p22_Entre 11 y 15 km`</t>
+          <t>`p23_agregado_Visitas sociales`</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>`p22_Entre 6 y 10 km`</t>
+          <t>`p23_agregado_Cuidado y familia`</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>`p22_Menos de 5 km`</t>
+          <t>p38p38_dummy_1</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
+          <t>`p19comuna_Comuna 13 - San Javier`</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>`p23_agregado_Compras y trámites`</t>
+          <t>`p19comuna_Comuna 15 - Guayabal`</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>p23_agregado_Estudio</t>
+          <t>`p19comuna_Comuna 3 - Manrique`</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>`p23_agregado_Visitas sociales`</t>
+          <t>`p19comuna_Comuna 6 - Doce de Octubre`</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>`p23_agregado_Cuidado y familia`</t>
+          <t>`p19comuna_Comuna 8 - Villa Hermosa`</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>p38p38_dummy_1</t>
+          <t>`p19comuna_Comuna 4 - Aranjuez`</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 13 - San Javier`</t>
+          <t>`p19comuna_Comuna 12 - La América`</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 15 - Guayabal`</t>
+          <t>`p19comuna_Comuna 1 - Popular`</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 3 - Manrique`</t>
+          <t>`p19comuna_Comuna 5 - Castilla`</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 6 - Doce de Octubre`</t>
+          <t>`p19comuna_Comuna 10 - La Candelaria`</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 8 - Villa Hermosa`</t>
+          <t>`p19comuna_Comuna 2 - Santa Cruz`</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 4 - Aranjuez`</t>
+          <t>`p19comuna_Comuna 7 - Robledo`</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 12 - La América`</t>
+          <t>`p19comuna_Comuna 9 - Buenos Aires`</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>`p19comuna_Comuna 1 - Popular`</t>
+          <t>`p19comuna_Comuna 11 - Laureles Estadio`</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>`p19comuna_Comuna 5 - Castilla`</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>`p19comuna_Comuna 10 - La Candelaria`</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>`p19comuna_Comuna 2 - Santa Cruz`</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>`p19comuna_Comuna 7 - Robledo`</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>`p19comuna_Comuna 9 - Buenos Aires`</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>`p19comuna_Comuna 11 - Laureles Estadio`</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>`p19comuna_Comuna 14 - El Poblado`</t>
         </is>
@@ -7131,69 +6499,67 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>4.301</v>
       </c>
       <c r="C2">
-        <v>1381786092.91</v>
+        <v>135.694</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="F2">
-        <v>2.098284978353452E+46</v>
+        <v>12.65</v>
       </c>
       <c r="G2">
-        <v>2.138566688511446E+95</v>
+        <v>2735823.156</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>6.179308370837537E+147</v>
+        <v>144682.04</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>4.713323760296749E+96</v>
+        <v>1559161566.739</v>
       </c>
       <c r="M2">
-        <v>4.886950918866695E+107</v>
+        <v>0.767</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.457</v>
       </c>
       <c r="O2">
-        <v>8551.587</v>
+        <v>1207.971</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>890363585.2130001</v>
       </c>
       <c r="Q2">
-        <v>1.723143609200713E+99</v>
+        <v>123.065</v>
       </c>
       <c r="R2">
-        <v>2.41478165029674E+209</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>31301152044319.31</v>
       </c>
       <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>151701000119118.3</v>
+      </c>
+      <c r="U2">
+        <v>9579588441.246</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>5.009531298099098E+17</v>
       </c>
       <c r="W2">
         <v>0</v>
@@ -7202,46 +6568,40 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>2.468626841919825E+181</v>
+        <v>8886.603999999999</v>
       </c>
       <c r="Z2">
-        <v>1.086047698480961E+39</v>
+        <v>3.017592729863068E+35</v>
       </c>
       <c r="AA2">
-        <v>2.248760080357771E+141</v>
+        <v>1.501268322447324E+54</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>6.23748983527558E+40</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>18.007</v>
       </c>
       <c r="AD2">
-        <v>9.23718287130113E+53</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>9.965941896830818E+80</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AH2">
+        <v>7197.355</v>
       </c>
       <c r="AI2">
-        <v>6.5757581906067E+137</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>515769.386</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -7250,45 +6610,43 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>2863664113.575</v>
+        <v>437131.434</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>1.699661552282557E+28</v>
       </c>
       <c r="AO2">
-        <v>0</v>
+        <v>1.689340795034315E+20</v>
       </c>
       <c r="AP2">
-        <v>5.870828869482544E+89</v>
+        <v>147666257.11</v>
       </c>
       <c r="AQ2">
-        <v>6.482927878203427E+93</v>
+        <v>0.111</v>
       </c>
       <c r="AR2">
         <v>0</v>
       </c>
       <c r="AS2">
-        <v>1.35217578588388E+87</v>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>5.287</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
       </c>
       <c r="AU2">
-        <v>1.283133820856334E+259</v>
+        <v>0</v>
       </c>
       <c r="AV2">
         <v>0</v>
       </c>
       <c r="AW2">
-        <v>1702.695</v>
+        <v>0</v>
       </c>
       <c r="AX2">
         <v>0</v>
       </c>
       <c r="AY2">
-        <v>2.880912757681664E+110</v>
+        <v>151134144.697</v>
       </c>
       <c r="AZ2">
         <v>0</v>
@@ -7297,24 +6655,6 @@
         <v>0</v>
       </c>
       <c r="BB2">
-        <v>6.260760251136052E+27</v>
-      </c>
-      <c r="BC2">
-        <v>0</v>
-      </c>
-      <c r="BD2">
-        <v>0</v>
-      </c>
-      <c r="BE2">
-        <v>4.482229763467052E+115</v>
-      </c>
-      <c r="BF2">
-        <v>0</v>
-      </c>
-      <c r="BG2">
-        <v>0</v>
-      </c>
-      <c r="BH2">
         <v>0</v>
       </c>
     </row>
@@ -7326,28 +6666,28 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>3.448437409877037E+50</v>
+        <v>689250.6629999999</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="G3">
-        <v>2.546588705862434E+38</v>
+        <v>548.955</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1.826</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>3.565030097590247E+121</v>
+        <v>512297425.902</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -7356,108 +6696,94 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>4.528074653279279E+96</v>
+        <v>2.132</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>0.663</v>
       </c>
       <c r="O3">
-        <v>1663754.105</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.079560961502148E+29</v>
       </c>
       <c r="Q3">
-        <v>4.687138715965342E+37</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>178.328</v>
+      </c>
+      <c r="R3">
+        <v>8339.186</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>9.892661257153154E+32</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>8640.074000000001</v>
       </c>
       <c r="U3">
-        <v>1.931391525612226E+239</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>2.05368847091556E+123</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>1.480621618042722E+31</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>6.979361230789776E+59</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>6.549140420270326E+148</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>370275621.123</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>7.141467595823132E+45</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>9.669189258174291E+36</v>
       </c>
       <c r="AD3">
-        <v>2.066976994146423E+219</v>
+        <v>3.55152218596461E+31</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AF3">
-        <v>1.011451759861834E+73</v>
+        <v>1.126619135158017E+19</v>
       </c>
       <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>1.088591136435389E+31</v>
+      </c>
+      <c r="AH3">
+        <v>91503808494684.66</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>199210940.411</v>
       </c>
       <c r="AK3">
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>5.545193676232433E+218</v>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>7.355816606408942E+22</v>
       </c>
       <c r="AN3">
-        <v>2.348082739930422E+94</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>22.129</v>
       </c>
       <c r="AP3">
-        <v>86265.689</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -7466,55 +6792,33 @@
         <v>0</v>
       </c>
       <c r="AS3">
-        <v>3.486253509250816E+183</v>
+        <v>0</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>15.613</v>
       </c>
       <c r="AU3">
         <v>0</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>42949227.726</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>9.34219247026471E+17</v>
       </c>
       <c r="AX3">
-        <v>7.991616138532294E+22</v>
+        <v>0</v>
       </c>
       <c r="AY3">
         <v>0</v>
       </c>
       <c r="AZ3">
-        <v>0</v>
+        <v>6326100465899.889</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="BB3">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="BD3">
-        <v>0</v>
-      </c>
-      <c r="BE3">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="BG3">
-        <v>0</v>
-      </c>
-      <c r="BH3">
         <v>0</v>
       </c>
     </row>
@@ -7526,128 +6830,118 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.226971011068175E+27</v>
+        <v>224.573</v>
       </c>
       <c r="D4">
-        <v>1.546010068638546E+17</v>
+        <v>2.619</v>
       </c>
       <c r="E4">
-        <v>2.306192261520744E+18</v>
+        <v>1001.462</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>2.110112703367868E+95</v>
+        <v>1200727.072</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J4">
-        <v>2.041104058624001E+115</v>
+        <v>1001077.873</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>4.565649121824321E+137</v>
+        <v>524047705.39</v>
       </c>
       <c r="M4">
-        <v>4.514933178200618E+70</v>
+        <v>0.668</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>5.425</v>
       </c>
       <c r="O4">
+        <v>3.794926233397736E+17</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>2380824489.422</v>
+      </c>
+      <c r="R4">
+        <v>1769.029</v>
+      </c>
+      <c r="S4">
+        <v>42830198902.546</v>
+      </c>
+      <c r="T4">
+        <v>33358459292.612</v>
+      </c>
+      <c r="U4">
+        <v>52452136922.217</v>
+      </c>
+      <c r="V4">
+        <v>1.429978048073484E+51</v>
+      </c>
+      <c r="W4">
         <v>0.001</v>
       </c>
-      <c r="P4">
-        <v>2139051942943.103</v>
-      </c>
-      <c r="Q4">
-        <v>1.992197350882711E+267</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>1.387749334576066E+278</v>
-      </c>
-      <c r="T4">
-        <v>7.029834069612236E+195</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>3.314114523237052E+212</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
       <c r="X4">
-        <v>1.094166254154498E+158</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>2.852122396130774E+49</v>
+        <v>2.202311868963328E+20</v>
       </c>
       <c r="Z4">
-        <v>5.328498072148561E+232</v>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>2416703.296</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.988603569197029E+20</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>1.867801535825337E+79</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>49376658327883.09</v>
+      </c>
+      <c r="AE4">
+        <v>49.373</v>
       </c>
       <c r="AF4">
-        <v>1.384183325392031E+165</v>
+        <v>687222403.149</v>
       </c>
       <c r="AG4">
-        <v>382495.387</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>21695.392</v>
+      </c>
+      <c r="AH4">
+        <v>1.444154130221228E+26</v>
       </c>
       <c r="AI4">
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>1.52435247248866E+94</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>3800342973642744</v>
       </c>
       <c r="AL4">
-        <v>3.284144205580605E+52</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>6.837028283255667E+49</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
       </c>
       <c r="AO4">
         <v>0</v>
@@ -7656,7 +6950,7 @@
         <v>0</v>
       </c>
       <c r="AQ4">
-        <v>3.114131768136859E+202</v>
+        <v>0</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -7665,7 +6959,7 @@
         <v>0</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>9.204908846176271E+27</v>
       </c>
       <c r="AU4">
         <v>0</v>
@@ -7674,40 +6968,22 @@
         <v>0</v>
       </c>
       <c r="AW4">
-        <v>1.970984807540822E+129</v>
+        <v>0</v>
       </c>
       <c r="AX4">
         <v>0</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>145426684.557</v>
       </c>
       <c r="AZ4">
-        <v>5.49491716100207E+270</v>
+        <v>0</v>
       </c>
       <c r="BA4">
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>1.330138620106585E+93</v>
-      </c>
-      <c r="BC4">
-        <v>0</v>
-      </c>
-      <c r="BD4">
-        <v>1963698148.876</v>
-      </c>
-      <c r="BE4">
-        <v>7.317527051859875E+144</v>
-      </c>
-      <c r="BF4">
-        <v>0</v>
-      </c>
-      <c r="BG4">
-        <v>0</v>
-      </c>
-      <c r="BH4">
-        <v>4.693294633677335E+100</v>
+        <v>172793359.901</v>
       </c>
     </row>
     <row r="5">
@@ -7718,7 +6994,7 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>1.078016121277751E+59</v>
+        <v>17988.144</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -7727,175 +7003,151 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H5">
-        <v>7.643191009821507E+36</v>
+        <v>216.493</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="J5">
-        <v>2.022410686910314E+84</v>
+        <v>2768478.774</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>1.492880515922753E+17</v>
+        <v>4.573</v>
       </c>
       <c r="M5">
-        <v>9.405642345402156E+54</v>
+        <v>3.616</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>4.477</v>
       </c>
       <c r="O5">
-        <v>4981438219.452</v>
+        <v>1.305917184056804E+21</v>
       </c>
       <c r="P5">
-        <v>33267159536.003</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>2.989</v>
+      </c>
+      <c r="Q5">
+        <v>192512265.477</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>1.457074701233078E+188</v>
+        <v>3839.69</v>
       </c>
       <c r="T5">
-        <v>3.405381785179212E+53</v>
+        <v>3.636655651126657E+18</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>21948611506821.29</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.153872331496017E+25</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>526675.067</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>76337.43799999999</v>
       </c>
       <c r="Y5">
-        <v>8.996804537763793E+154</v>
+        <v>111678.895</v>
       </c>
       <c r="Z5">
-        <v>1.888479476393311E+223</v>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.653588846282818E+65</v>
+        <v>468779331885.269</v>
       </c>
       <c r="AC5">
-        <v>4.496183531075771E+35</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>1.572632608653239E+66</v>
+        <v>3277.762</v>
       </c>
       <c r="AE5">
-        <v>1.939229421328143E+118</v>
+        <v>1.352</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>340627702.732</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>9074981563946.273</v>
       </c>
       <c r="AH5">
-        <v>1.861202259864672E+194</v>
+        <v>675202923382.474</v>
       </c>
       <c r="AI5">
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>4082751836.567</v>
+        <v>336.806</v>
       </c>
       <c r="AK5">
         <v>0</v>
       </c>
       <c r="AL5">
-        <v>7.665826847094243E+112</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>1.749900054879473E+181</v>
+        <v>0.001</v>
       </c>
       <c r="AN5">
-        <v>2.05185916212994E+215</v>
+        <v>1.331541627663602E+26</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>93.46599999999999</v>
       </c>
       <c r="AP5">
-        <v>2.717721685202878E+99</v>
+        <v>179.076</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>62.444</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="AS5">
         <v>0</v>
       </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+      <c r="AT5">
+        <v>5.011957584879756E+24</v>
       </c>
       <c r="AU5">
         <v>0</v>
       </c>
       <c r="AV5">
-        <v>28289429.883</v>
+        <v>7.129640556784117E+20</v>
       </c>
       <c r="AW5">
-        <v>112.182</v>
+        <v>1221544311.506</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>298967.934</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>99433.70699999999</v>
       </c>
       <c r="AZ5">
-        <v>2.430679447616861E+152</v>
+        <v>32525.845</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>571538.571</v>
       </c>
       <c r="BB5">
-        <v>5.280349681095342E+196</v>
-      </c>
-      <c r="BC5">
-        <v>4605569.838</v>
-      </c>
-      <c r="BD5">
-        <v>0.001</v>
-      </c>
-      <c r="BE5">
-        <v>1.150275039982081E+68</v>
-      </c>
-      <c r="BF5">
-        <v>2.884131574023628E+166</v>
-      </c>
-      <c r="BG5">
-        <v>1938132633182.383</v>
-      </c>
-      <c r="BH5">
-        <v>1.172933073772021E+189</v>
+        <v>2.106051854817797E+17</v>
       </c>
     </row>
   </sheetData>
